--- a/data/xlsx/gleif.xlsx
+++ b/data/xlsx/gleif.xlsx
@@ -885,7 +885,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5299GWCS8O4K0GWCS867</t>
+          <t>6299GWCS8O4K0GWCS867</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>SISUED</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1737,7 +1737,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6299M8UG2OAWI4QCYK86</t>
+          <t>5299M8UG2OAWI4QCYK86</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>5299KGC840WSOKGC8447</t>
+          <t>6299KGC840WSOKGC8447</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6299QSUWY02468ACEG83</t>
+          <t>5299QSUWY02468ACEG83</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>5299O0CO0CO0CO0CO050</t>
+          <t>6299O0CO0CO0CO0CO050</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>6299UCUCUCUCUCUCUC27</t>
+          <t>5299UCUCUCUCUCUCUC27</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -7843,7 +7843,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5299ZSLE70TMF81UNG45</t>
+          <t>6299ZSLE70TMF81UNG45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>PARTIALL_CORROBORATED</t>
+          <t>PRATIALL_CORROBORATED</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>ACTVIE</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8695,7 +8695,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6299543210ZYXWVUTS73</t>
+          <t>5299543210ZYXWVUTS73</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>52993CLU3CLU3CLU3C42</t>
+          <t>62993CLU3CLU3CLU3C42</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>62999O3IXCR6L0FU9O92</t>
+          <t>52999O3IXCR6L0FU9O92</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>52997WLAZOD2RG5UJ835</t>
+          <t>62997WLAZOD2RG5UJ835</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>6299D83YTOJE94ZUPK91</t>
+          <t>5299D83YTOJE94ZUPK91</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
@@ -14801,7 +14801,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5299IOU06CIOU06CIO52</t>
+          <t>6299IOU06CIOU06CIO52</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>FULLY_CORROOBRATED</t>
+          <t>FULLY_CORROBORATED</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTVIE</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -15653,7 +15653,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>6299O0CO0CO0CO0CO050</t>
+          <t>5299O0CO0CO0CO0CO050</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -17153,7 +17153,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>5299M8UG2OAWI4QCYK86</t>
+          <t>6299M8UG2OAWI4QCYK86</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -18005,7 +18005,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>6299SKC4WOG80SKC4W71</t>
+          <t>5299SKC4WOG80SKC4W71</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>5299QSUWY02468ACEG83</t>
+          <t>6299QSUWY02468ACEG83</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
@@ -20307,7 +20307,7 @@
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>6299W4CKS08GOW4CKS62</t>
+          <t>5299W4CKS08GOW4CKS62</t>
         </is>
       </c>
       <c r="X143" t="inlineStr">
@@ -21759,7 +21759,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>52991K3M5O7Q9SBUDW28</t>
+          <t>62991K3M5O7Q9SBUDW28</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -22534,7 +22534,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>PARTIALLY_CORROBORATED</t>
+          <t>PARTIALLY_CORORBORATED</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -22611,7 +22611,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>62997WLAZOD2RG5UJ835</t>
+          <t>52997WLAZOD2RG5UJ835</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>5299543210ZYXWVUTS73</t>
+          <t>6299543210ZYXWVUTS73</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -24963,7 +24963,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>6299BGLQV05AFKPUZ498</t>
+          <t>5299BGLQV05AFKPUZ498</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>52999O3IXCR6L0FU9O92</t>
+          <t>62999O3IXCR6L0FU9O92</t>
         </is>
       </c>
       <c r="X186" t="inlineStr">
@@ -27265,7 +27265,7 @@
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>6299F0L6RCXI3O9UF057</t>
+          <t>5299F0L6RCXI3O9UF057</t>
         </is>
       </c>
       <c r="X192" t="inlineStr">

--- a/data/xlsx/gleif.xlsx
+++ b/data/xlsx/gleif.xlsx
@@ -215,12 +215,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2015-24-12</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -275,7 +275,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -310,7 +310,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
     </row>
@@ -322,7 +322,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Polskie Przetwory sp z oo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -357,12 +357,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20160103</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -464,7 +464,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o. o.</t>
+          <t>Hurtownia Nabiału Mleczko sp. z o. o.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -499,12 +499,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10/02/2017</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lumen Advisory Sp. z o.o.</t>
+          <t>Agencja Reklamowa Kreatywni Sp. z o.o.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2018/17/03</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-01-03</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nova Data SP Z O O</t>
+          <t>Kancelaria Prawna Sankcja SP Z O O</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24-04-2019</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0000000396</t>
+          <t>000000039</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -885,12 +885,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6299GWCS8O4K0GWCS867</t>
+          <t>5299GWCS8O4K0GWCS867</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Śląskie Zakłady Mechaniczne spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-26-12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Fabryka Okien i Drzwi Profil Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20210610</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quantum Services S.A.</t>
+          <t>Przedsiębiorstwo Robót Drogowych S.A.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bydgo</t>
+          <t>Bdygo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SISUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17/07/2022</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>529900T8BM49AURSDO55</t>
+          <t>529900T8BM49UARSDO55</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>IS_DIRECTLY_CONSOLIDATED_BY</t>
+          <t>IS_DIRECLTY_CONSOLIDATED_BY</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Silesia Invest SA</t>
+          <t>Krakowskie Biuro Nieruchomości SA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2023/24/08</t>
+          <t>2023/19/03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vistula Fintech S. A.</t>
+          <t>Salon Samochodowy Auto-Hit S. A.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>03-09-2024</t>
+          <t>26-04-2024</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka Akcyjna</t>
+          <t>Klinika Stomatologiczna Dent-Med Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1635,12 +1635,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Polski Tytoń sp. z o.o.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>20261117</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>335834938</t>
+          <t>235834938</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Gdańska Stocznia Jachtowa sp z oo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>24/12/2015</t>
+          <t>19/07/2015</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
+          <t>2015-08-04</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o. o.</t>
+          <t>Wytwórnia Makaronu Jajecznego sp. z o. o.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2016/03/01</t>
+          <t>2016/26/08</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nova Data Sp. z o.o.</t>
+          <t>Zakłady Mięsne Tradycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2203,17 +2203,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>10-02-2017</t>
+          <t>05-09-2017</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2017-01-05</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optima Trade SP Z O O</t>
+          <t>Spółdzielnia Mleczarska Radomsko SP Z O O</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2345,12 +2345,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2018-17-03</t>
+          <t>2018-12-10</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Polaris Capital spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kancelaria Finansowo-Księgowa Bilans spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20190424</t>
+          <t>20191119</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zarząd Nieruchomości Komercyjnych Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2629,64 +2629,64 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>26/12/2020</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2020/22/08</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>23-09-2020</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>03/05/2020</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2020/22/08</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>23-09-2020</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>National Official Business Register (Central Statistical Office) | Krajowy Rejestr Urzedowy Podmiotow Gospodarki Narodowej REGON (Glowny Urzad Statystyczny) | Poland | RA000484</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>236310077</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>5299SKC4WOG80SKC4W71</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>National Official Business Register (Central Statistical Office) | Krajowy Rejestr Urzedowy Podmiotow Gospodarki Narodowej REGON (Glowny Urzad Statystyczny) | Poland | RA000484</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>236310077</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>5299SKC4WOG80SKC4W71</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>13/03/2020</t>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-01-11</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Silesia Invest S.A.</t>
+          <t>Polskie Linie Oceaniczne S.A.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2021/10/06</t>
+          <t>2021/05/01</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vistula Fintech SA</t>
+          <t>Hurtownia Materiałów Budowlanych Cegiełka SA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Piłsudskiego 84, Rzeszów</t>
+          <t>Rynek 84, Opole</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>17-07-2022</t>
+          <t>12-02-2022</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Studio Projektowe Architektura</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2023-24-08</t>
+          <t>2023-19-03</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka Akcyjna</t>
+          <t>Centrum Medycyny Pracy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>20240903</t>
+          <t>20240426</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>6299KGC840WSOKGC8447</t>
+          <t>5299KGC840WSOKGC8447</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o.o.</t>
+          <t>Przedsiębiorstwo Energetyki Cieplnej sp. z o.o.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3339,12 +3339,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp z oo</t>
+          <t>Gospodarstwo Rolno-Ogrodnicze sp z oo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026/17/11</t>
+          <t>2026/12/06</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o. o.</t>
+          <t>Drukarnia Wielkoformatowa Impress sp. z o. o.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>24-12-2015</t>
+          <t>19-07-2015</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optima Trade Sp. z o.o.</t>
+          <t>Klub Fitness Sylwetka Sp. z o.o.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-26-08</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Polska Grupa Energetyczna SP Z O O</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>20170210</t>
+          <t>20170905</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Quantum Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Mazowieckie Zakłady Drobiarskie spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>17/03/2018</t>
+          <t>12/10/2018</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Hurtownia Farmaceutyczna Aptekarz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2019/24/04</t>
+          <t>2019/19/11</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2019-08-04</t>
+          <t>2019-04-08</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Kancelaria Notarialna Lex S.A.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>03-05-2020</t>
+          <t>26-12-2020</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Astra Finance SA</t>
+          <t>Biuro Podróży Wojażer SA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4475,12 +4475,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S. A.</t>
+          <t>Szkoła Języków Obcych Lingua S. A.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>20220717</t>
+          <t>20220212</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka Akcyjna</t>
+          <t>Centrum Logistyczne Podlasie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>24/08/2023</t>
+          <t>19/03/2023</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o.o.</t>
+          <t>Fabryka Mebli Drewnianych Dąb sp. z o.o.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2024/03/09</t>
+          <t>2024/26/04</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Polskie Sady sp z oo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>10-10-2025</t>
+          <t>05-05-2025</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o. o.</t>
+          <t>Wielkopolska Hurtownia Stali sp. z o. o.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-17-11</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Polaris Capital Sp. z o.o.</t>
+          <t>Zakład Oczyszczania Miasta Sp. z o.o.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>20151224</t>
+          <t>20150719</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Quantum Services SP Z O O</t>
+          <t>Przedsiębiorstwo Wodociągów i Kanalizacji SP Z O O</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>57-300 Kłodzko</t>
+          <t>70-435 Szczecin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>57-300</t>
+          <t>70-435</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>03/01/2016</t>
+          <t>26/08/2016</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2016-11-09</t>
+          <t>2016-09-11</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>6299O0CO0CO0CO0CO050</t>
+          <t>5299O0CO0CO0CO0CO050</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Silesia Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Instytut Badań Rynkowych spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2017/10/02</t>
+          <t>2017/05/09</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2017-02-06</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Agencja Ochrony Solidna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5753,17 +5753,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>17-03-2018</t>
+          <t>12-10-2018</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2019-24-04</t>
+          <t>2019-19-11</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-02-06</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-02-06</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SA</t>
+          <t>Krajowa Izba Gospodarcza SA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>20200503</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Helios Markets S. A.</t>
+          <t>Polskie Zakłady Lotnicze S. A.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>10/06/2021</t>
+          <t>05/01/2021</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>Hurtownia Elektryczna Wat Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2022/17/07</t>
+          <t>2022/12/02</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-01-07</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o.o.</t>
+          <t>Centrum Ogrodnicze Zielona Oaza sp. z o.o.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>24-08-2023</t>
+          <t>19-03-2023</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Piekarnia i Cukiernia Chrupiący Rogalik sp z oo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-26-04</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o. o.</t>
+          <t>Zakład Usług Komunalnych sp. z o. o.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>20251010</t>
+          <t>20250505</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Quantum Services Sp. z o.o.</t>
+          <t>Polski Komfort Sp. z o.o.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>17/11/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Kancelaria Radców Prawnych Partnerzy SP Z O O</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2015/24/12</t>
+          <t>2015/19/07</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
+          <t>2015-12-08</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vistula Fintech spółka z ograniczoną odpowiedzialnością</t>
+          <t>Centrum Dystrybucji Alkoholi spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>03-01-2016</t>
+          <t>26-08-2016</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Przedsiębiorstwo Spedycyjne Ładunek Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2017-10-02</t>
+          <t>2017-05-09</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Fabryka Tekstyliów Splot S.A.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>20180317</t>
+          <t>20181012</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Helios Markets SA</t>
+          <t>Górnośląskie Towarzystwo Finansowe SA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>24/04/2019</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2019-04-12</t>
+          <t>2019-12-04</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Lumen Advisory S. A.</t>
+          <t>Krajowa Agencja Informacyjna S. A.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2020/03/05</t>
+          <t>2020/26/12</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>239160916</t>
+          <t>339160916</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -7843,12 +7843,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6299ZSLE70TMF81UNG45</t>
+          <t>5299ZSLE70TMF81UNG45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Polskie Jagody Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7883,17 +7883,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>10-06-2021</t>
+          <t>05-01-2021</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2021-01-09</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o.o.</t>
+          <t>Zielony Amber sp. z o.o.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2022-17-07</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Zielony Bizon sp z oo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8167,12 +8167,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2023-08-24T07:55:39Z</t>
+          <t>2023-03-19T07:55:39Z</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o. o.</t>
+          <t>Zielnoy Canyon sp. z o. o.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>03/09/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>IS_ULTIMATELY_CONSLOIADTED_BY</t>
+          <t>IS_ULTIMATELY_CONSLOIDATED_BY</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Silesia Invest Sp. z o.o.</t>
+          <t>Zielony Delfin Sp. z o.o.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2025/10/10</t>
+          <t>2025/05/05</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Vistula Fintech SP Z O O</t>
+          <t>Zielony Echo SP Z O O</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8593,17 +8593,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>17-11-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>P.P.H.U. Astra Finance</t>
+          <t>P.P.H.U. Zielony Falcon</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2015-24-12</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Gryf Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>20160103</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>339794437</t>
+          <t>239794437</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>5299CCCCCCCCCCCCCC47</t>
+          <t>6299CCCCCCCCCCCCCC47</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Zielony Horyzont S.A.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>10/02/2017</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lumen Advisory SA</t>
+          <t>Zielony Ikar SA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2018/17/03</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2018-01-03</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nova Data S. A.</t>
+          <t>Zielony Jantar S. A.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9303,12 +9303,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>24-04-2019</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Zielony Koral Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-26-12</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Zielony Lotos sp. z o.o.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 43, 00-590 Warszawa</t>
+          <t>ulica Chmielna 43, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>00-590</t>
+          <t>00-020</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>20210610</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -9694,12 +9694,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Zielony Magnolia sp z oo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 60, 00-071 Warszawa</t>
+          <t>Nowy Świat 60, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>00-071</t>
+          <t>00-029</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -9729,12 +9729,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>17/07/2022</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -9836,12 +9836,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o. o.</t>
+          <t>Zielony Neon sp. z o. o.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ul. Floriańska 77/75, 31-019 Kraków</t>
+          <t>ul. os. Przyjaźń 77/75, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>31-019</t>
+          <t>01-355</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2023/24/08</t>
+          <t>2023/19/03</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Vistula Fintech Sp. z o.o.</t>
+          <t>Zielony Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ul Długa 94, 31-147 Kraków</t>
+          <t>ul Jagiellońska 94, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>31-147</t>
+          <t>05-120</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>03-09-2024</t>
+          <t>26-04-2024</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -10120,12 +10120,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Astra Finance SP Z O O</t>
+          <t>Zielony Pegaz SP Z O O</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ulica Piotrkowska 111, 90-102 Łódź</t>
+          <t>ulica Piłsudskiego 111, 05-270 Marki</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>90-102</t>
+          <t>05-270</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -10155,12 +10155,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>62993CLU3CLU3CLU3C42</t>
+          <t>52993CLU3CLU3CLU3C42</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -10262,12 +10262,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Baltic Med Supply spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Zachodnia 128, 90-402 Łódź</t>
+          <t>Andriollego 128, 05-400 Otwock</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>90-402</t>
+          <t>05-400</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -10297,12 +10297,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>20261117</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Szafir Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ul. Świdnicka 145/37, 50-066 Wrocław</t>
+          <t>ul. Żeromskiego 145/37, 26-600 Radom</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>50-066</t>
+          <t>26-600</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -10439,12 +10439,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>24/12/2015</t>
+          <t>19/07/2015</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
+          <t>2015-08-04</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Zielony Tytan S.A.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ul Legnicka 162, 54-203 Wrocław</t>
+          <t>ul Tumska 162, 09-402 Płock</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>54-203</t>
+          <t>09-402</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2016/03/01</t>
+          <t>2016/26/08</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nova Data SA</t>
+          <t>Zielony Uran SA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ulica Święty Marcin 179, 61-806 Poznań</t>
+          <t>ulica Karmelicka 179, 31-128 Kraków</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>61-806</t>
+          <t>31-128</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -10723,17 +10723,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>10-02-2017</t>
+          <t>05-09-2017</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2017-01-05</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Optima Trade S. A.</t>
+          <t>Zielony Wektor S. A.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Głogowska 16, 60-734 Poznań</t>
+          <t>os. Na Stoku 16, 31-704 Kraków</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>60-734</t>
+          <t>31-704</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2018-17-03</t>
+          <t>2018-12-10</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -10972,12 +10972,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka Akcyjna</t>
+          <t>Zielony Zefir Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ul. Długa 33/89, 80-831 Gdańsk</t>
+          <t>ul. Krupówki 33/89, 34-500 Zakopane</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>80-831</t>
+          <t>34-500</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>20190424</t>
+          <t>20191119</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Zielony Żubr sp. z o.o.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ul Grunwaldzka 50, 80-236 Gdańsk</t>
+          <t>50, 34-600 Mordarka</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>80-236</t>
+          <t>34-600</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>03/05/2020</t>
+          <t>26/12/2020</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-01-11</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -11256,12 +11256,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Zielony Sokół sp z oo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 67, 70-435 Szczecin</t>
+          <t>ulica Galicyjska 67, 32-087 Zielonki</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>70-435</t>
+          <t>32-087</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -11291,12 +11291,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2021/10/06</t>
+          <t>2021/05/01</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o. o.</t>
+          <t>Zielony Orzeł sp. z o. o.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wyszyńskiego 84, 70-200 Szczecin</t>
+          <t>84, 32-003 Podłęże</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>70-200</t>
+          <t>32-003</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -11433,17 +11433,17 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>17-07-2022</t>
+          <t>12-02-2022</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ul. Mariacka 101/51, 40-014 Katowice</t>
+          <t>ul. Wałowa 101/51, 33-100 Tarnów</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>40-014</t>
+          <t>33-100</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -11575,12 +11575,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2023-24-08</t>
+          <t>2023-19-03</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -11682,12 +11682,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Zielony Barycz SP Z O O</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ul Warszawska 118, 40-009 Katowice</t>
+          <t>ul Narutowicza 118, 90-135 Łódź</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>40-009</t>
+          <t>90-135</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -11717,12 +11717,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>20240903</t>
+          <t>20240426</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>241457425</t>
+          <t>251378267</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Noteć spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ulica Krakowskie Przedmieście 135, 20-002 Lublin</t>
+          <t>ulica os. Retkinia 135, 94-004 Łódź</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20-002</t>
+          <t>94-004</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -11909,52 +11909,52 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
+          <t>IS_DIRECTLY_CONSOLIDATED_BY</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2025-18-06</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>5299F0L6RCXI3O9UF057</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>20/08/2025</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>2025-18-06</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>5299F0L6RCXI3O9UF057</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>IS_ULTIMATELY_CONSOLIDATED_BY</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>22-10-2025</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
         <is>
           <t/>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>IS_ULTIMATELY_CONSOLIDATED_BY</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>22-10-2025</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>20/08/2025</t>
         </is>
       </c>
     </row>
@@ -11966,12 +11966,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Pilica Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chełmińska 92, 87-100</t>
+          <t>Piastowska 92, 48-300</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>87-100</t>
+          <t>48-300</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026/17/11</t>
+          <t>2026/12/06</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
@@ -12108,12 +12108,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nova Data S.A.</t>
+          <t>Zielony Narew S.A.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ul. Lipowa 169/13, 15-424 Białystok</t>
+          <t>ul. Długa 169/13, 95-100 Zgierz</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>15-424</t>
+          <t>95-100</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>24-12-2015</t>
+          <t>19-07-2015</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -12250,12 +12250,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Optima Trade SA</t>
+          <t>Zielony Jodełka SA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 6, 15-092 Białystok</t>
+          <t>ul Rynek 6, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>15-092</t>
+          <t>50-101</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -12285,12 +12285,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-26-08</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -12392,12 +12392,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Polaris Capital S. A.</t>
+          <t>Zielony Kaktus S. A.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ulica Gdańska 23, 85-005 Bydgoszcz</t>
+          <t>ulica Jedności Narodowej 23, 50-260 Wrocław</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>85-005</t>
+          <t>50-260</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -12427,12 +12427,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>20170210</t>
+          <t>20170905</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>62997WLAZOD2RG5UJ835</t>
+          <t>52997WLAZOD2RG5UJ835</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka Akcyjna</t>
+          <t>Zielony Szmaragd Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>os. Dworcowa 40, 85-009 Bydgoszcz</t>
+          <t>os. Konstytucji 3 Maja 40, 58-540 Karpacz</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>85-009</t>
+          <t>58-540</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -12569,12 +12569,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>17/03/2018</t>
+          <t>12/10/2018</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -12676,12 +12676,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Zielony Topaz sp. z o.o.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ul. Szeroka 57/65, 87-100 Toruń</t>
+          <t>ul. Odrodzenia 57/65, 59-300 Lubin</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>87-100</t>
+          <t>59-300</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -12711,12 +12711,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2019/24/04</t>
+          <t>2019/19/11</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2019-08-04</t>
+          <t>2019-04-08</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
@@ -12818,12 +12818,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Zielony Granit sp z oo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ul Chełmińska 74, 87-100 Toruń</t>
+          <t>ul Słowackiego 74, 58-300 Wałbrzych</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>87-100</t>
+          <t>58-300</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>03-05-2020</t>
+          <t>26-12-2020</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>242090949</t>
+          <t>252011787</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -12960,12 +12960,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Astra Finance sp. z o. o.</t>
+          <t>Zielony Marmur sp. z o. o.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 91, 35-030 Rzeszów</t>
+          <t>ulica Półwiejska 91, 61-888 Poznań</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>35-030</t>
+          <t>61-888</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -12995,12 +12995,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -13102,12 +13102,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Sp. z o.o.</t>
+          <t>Zielony Syrena Sp. z o.o.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Piłsudskiego 108, 35-074 Rzeszów</t>
+          <t>os. Bolesława Chrobrego 108, 60-681 Poznań</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>35-074</t>
+          <t>60-681</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -13137,12 +13137,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>20220717</t>
+          <t>20220212</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Helios Markets SP Z O O</t>
+          <t>Zielony Zodiak SP Z O O</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 125/27, 25-007 Kielce</t>
+          <t>ul. Główny Rynek 125/27, 62-800 Kalisz</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>25-007</t>
+          <t>62-800</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -13279,12 +13279,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>24/08/2023</t>
+          <t>19/03/2023</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Olimp spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ul Warszawska 142, 25-512 Kielce</t>
+          <t>ul Kaliska 142, 63-400 Ostrów Wielkopolski</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>25-512</t>
+          <t>63-400</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -13421,12 +13421,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2024/03/09</t>
+          <t>2024/26/04</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nova Data Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Zorza Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 159, 10-504 Olsztyn</t>
+          <t>ulica Ogarna 159, 80-826 Gdańsk</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>10-504</t>
+          <t>80-826</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>10-10-2025</t>
+          <t>05-05-2025</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -13670,12 +13670,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Optima Trade S.A.</t>
+          <t>Zielony Krokus S.A.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dąbrowszczaków 176, 10-540 Olsztyn</t>
+          <t>os. Jasień 176, 80-180 Gdańsk</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>10-540</t>
+          <t>80-180</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-17-11</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>242566085</t>
+          <t>252486929</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -13812,12 +13812,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Polaris Capital SA</t>
+          <t>Zielony Narcyz SA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ul. Krakowska 13/79, 45-018 Opole</t>
+          <t>ul. Bohaterów Monte Cassino 13/79, 81-759 Sopot</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>45-018</t>
+          <t>81-759</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -13847,12 +13847,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>20151224</t>
+          <t>20150719</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Quantum Services S. A.</t>
+          <t>Zielony Giewont S. A.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ul Ozimska 30, 45-057 Opole</t>
+          <t>30, 80-209 Chwaszczyno</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>45-057</t>
+          <t>80-209</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -13989,12 +13989,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>03/01/2016</t>
+          <t>26/08/2016</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2016-11-09</t>
+          <t>2016-09-11</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
@@ -14096,12 +14096,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka Akcyjna</t>
+          <t>Zielony Rysy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ulica Bohaterów Westerplatte 47, 65-034 Zielona Góra</t>
+          <t>ulica 3 Maja 47, 40-096 Katowice</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>65-034</t>
+          <t>40-096</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -14131,12 +14131,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2017/10/02</t>
+          <t>2017/05/09</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2017-02-06</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -14238,12 +14238,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o.o.</t>
+          <t>Zielony Kasprowy sp. z o.o.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kupiecka 64, 65-058 Zielona Góra</t>
+          <t>os. Paderewskiego 64, 40-282 Katowice</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>65-058</t>
+          <t>40-282</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -14273,17 +14273,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>17-03-2018</t>
+          <t>12-10-2018</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -14380,12 +14380,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Zielony Beskid</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ul. Świętojańska 81/41, 81-372 Gdynia</t>
+          <t>ul. Zwycięstwa 81/41, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>81-372</t>
+          <t>44-100</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -14415,12 +14415,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2019-24-04</t>
+          <t>2019-19-11</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-02-06</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-02-06</t>
         </is>
       </c>
     </row>
@@ -14522,12 +14522,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o. o.</t>
+          <t>Zielony Bieszczady sp. z o. o.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 38</t>
+          <t>ul Krupówki 38</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -14557,12 +14557,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>20200503</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -14664,12 +14664,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Helios Markets Sp. z o.o.</t>
+          <t>Zielony Karpaty Sp. z o.o.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ulica Bolesława Prusa 115, 05-800 Pruszków</t>
+          <t>ulica Najświętszej Maryi Panny 115, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>05-800</t>
+          <t>42-200</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>10/06/2021</t>
+          <t>05/01/2021</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -14734,7 +14734,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>0000009902</t>
+          <t>000000990</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -14801,17 +14801,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>6299IOU06CIOU06CIO52</t>
+          <t>5299IOU06CIOU06CIO52</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lumen Advisory SP Z O O</t>
+          <t>Zielony Bałtyk SP Z O O</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Kościuszki 132, 05-500 Piaseczno</t>
+          <t>11 Listopada 132, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>05-500</t>
+          <t>43-300</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -14841,12 +14841,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2022/17/07</t>
+          <t>2022/12/02</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2022-01-07</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
@@ -14948,12 +14948,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nova Data spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Sudety spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 149/3, 32-020 Wieliczka</t>
+          <t>149/3, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>32-020</t>
+          <t>36-047</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -14983,12 +14983,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>24-08-2023</t>
+          <t>19-03-2023</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -15090,12 +15090,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ul Dąbrowskiego 166, 32-600 Oświęcim</t>
+          <t>ul Franciszkańska 166, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>32-600</t>
+          <t>37-700</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -15125,12 +15125,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-26-04</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -15232,12 +15232,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Polaris Capital S.A.</t>
+          <t>Niebieski Bizon S.A.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ulica Rynek 3, 38-400 Krosno</t>
+          <t>ulica Kościuszki 3, 38-500 Sanok</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15247,7 +15247,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>38-400</t>
+          <t>38-500</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -15267,12 +15267,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>20251010</t>
+          <t>20250505</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -15374,12 +15374,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Quantum Services SA</t>
+          <t>Niebieski Canyon SA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Mickiewicza 20, 39-300 Mielec</t>
+          <t>Suraska 20, 15-422 Białystok</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>39-300</t>
+          <t>15-422</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -15409,12 +15409,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>17/11/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>IS_DIRECTLY_CONSOLIDATED_BY</t>
+          <t>IS_DIRECLTY_CONSOLIDATED_BY</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
@@ -15516,12 +15516,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Silesia Invest S. A.</t>
+          <t>Niebieski Delfin S. A.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ul. Długa 37/55, 58-100 Świdnica</t>
+          <t>37/55, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15531,7 +15531,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>58-100</t>
+          <t>16-030</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -15551,12 +15551,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2015/24/12</t>
+          <t>2015/19/07</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
+          <t>2015-12-08</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
@@ -15658,12 +15658,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka Akcyjna</t>
+          <t>Niebieski Echo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ul Wojska Polskiego 54, 57-300 Kłodzko</t>
+          <t>ul 3 Maja 54, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15673,7 +15673,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>57-300</t>
+          <t>17-200</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -15693,12 +15693,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>03-01-2016</t>
+          <t>26-08-2016</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -15800,12 +15800,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Astra Finance sp. z o.o.</t>
+          <t>Niebieski Falcon sp. z o.o.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ulica Chrobrego 71, 62-200 Gniezno</t>
+          <t>ulica os. LSM 71, 20-400 Lublin</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15815,7 +15815,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>62-200</t>
+          <t>20-400</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2017-10-02</t>
+          <t>2017-05-09</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -15942,12 +15942,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Niebieski Gryf sp z oo</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Słowiańska 88, 64-100 Leszno</t>
+          <t>88, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>64-100</t>
+          <t>24-120</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -15977,12 +15977,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>20180317</t>
+          <t>20181012</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -16012,7 +16012,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>343753932</t>
+          <t>243753932</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -16084,12 +16084,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o. o.</t>
+          <t>Niebieski Horyzont sp. z o. o.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>105/17, 83-110 Tczew</t>
+          <t>ul. Brzeska 105/17, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>83-110</t>
+          <t>21-500</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -16119,12 +16119,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>24/04/2019</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>2019-04-12</t>
+          <t>2019-12-04</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
@@ -16226,12 +16226,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lumen Advisory Sp. z o.o.</t>
+          <t>Niebieski Ikar Sp. z o.o.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ul Sobieskiego 122, 84-200 Wejherowo</t>
+          <t>ul Rynek Staromiejski 122, 87-100 Toruń</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>84-200</t>
+          <t>87-100</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -16261,12 +16261,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>2020/03/05</t>
+          <t>2020/26/12</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -16368,12 +16368,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nova Data SP Z O O</t>
+          <t>Niebieski Jantar SP Z O O</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ulica Głęboka 139, 43-400 Cieszyn</t>
+          <t>ulica Mostowa 139, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>43-400</t>
+          <t>85-110</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -16403,17 +16403,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>10-06-2021</t>
+          <t>05-01-2021</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2021-01-09</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Koral spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Małachowskiego 156, 42-500 Będzin</t>
+          <t>Stare Miasto 156, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16525,7 +16525,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>42-500</t>
+          <t>10-026</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -16545,12 +16545,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2022-17-07</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Lotos Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>os. Królowej Jadwigi 173/69, 88-100 Inowrocław</t>
+          <t>os. Warszawska 173/69, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -16667,7 +16667,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>88-100</t>
+          <t>11-700</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>20230824</t>
+          <t>20230319</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -16794,12 +16794,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quantum Services S.A.</t>
+          <t>Niebieski Magnolia S.A.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ul Wybickiego 10, 86-300 Grudziądz</t>
+          <t>ul Wojska Polskiego 10, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16809,7 +16809,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>86-300</t>
+          <t>70-470</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -16829,12 +16829,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>03/09/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Silesia Invest SA</t>
+          <t>Niebieski Neon SA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -16971,12 +16971,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>2025/10/10</t>
+          <t>2025/05/05</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -17078,12 +17078,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Vistula Fintech S. A.</t>
+          <t>Niebieski Oaza S. A.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Długa 164, Brzeg</t>
+          <t>Ogarna 164, Gdańsk</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -17113,17 +17113,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>17-11-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -17153,7 +17153,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>6299M8UG2OAWI4QCYK86</t>
+          <t>5299M8UG2OAWI4QCYK86</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ul. Lubelska 61/31, 24-100 Puławy</t>
+          <t>ul. Byczyńska 61/31, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17235,7 +17235,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>24-100</t>
+          <t>46-200</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -17255,12 +17255,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>2015-24-12</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -17315,7 +17315,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -17350,7 +17350,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
     </row>
@@ -17362,12 +17362,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Niebieski Rubin sp. z o.o.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ul Staszica 78, 22-400 Zamość</t>
+          <t>ul Chrobrego 78, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -17377,7 +17377,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>22-400</t>
+          <t>66-400</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -17397,12 +17397,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>20160103</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -17504,12 +17504,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Niebieski Szafir sp z oo</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 95, 16-300 Augustów</t>
+          <t>ulica 30 Stycznia 95, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17519,7 +17519,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>16-300</t>
+          <t>66-300</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -17539,12 +17539,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>10/02/2017</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -17646,12 +17646,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o. o.</t>
+          <t>Niebieski Tytan sp. z o. o.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Kościuszki 112, 16-400 Suwałki</t>
+          <t>Paderewskiego 112, 25-004 Kielce</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>16-400</t>
+          <t>25-004</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -17681,12 +17681,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>2018/17/03</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -17696,7 +17696,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>244783409</t>
+          <t>254704247</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -17771,7 +17771,7 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2018-01-03</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
@@ -17788,12 +17788,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Nova Data Sp. z o.o.</t>
+          <t>Niebieski Uran Sp. z o.o.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ul. Piastowska 129/83, 48-300 Nysa</t>
+          <t>ul. 1 Maja 129/83, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17803,7 +17803,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>48-300</t>
+          <t>28-100</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -17823,12 +17823,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>24-04-2019</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -17930,12 +17930,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Optima Trade SP Z O O</t>
+          <t>Niebieski Wektor SP Z O O</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ul Długa 146, 49-300 Brzeg</t>
+          <t>ul Marszałkowska 146, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17945,7 +17945,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>49-300</t>
+          <t>00-590</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -17965,12 +17965,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-26-12</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Polaris Capital spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Zefir spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>163, 68-200 Żary</t>
+          <t>ulica Krakowskie Przedmieście 163, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>68-200</t>
+          <t>00-071</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -18107,12 +18107,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>20210610</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -18214,12 +18214,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Żubr Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Sikorskiego 180, 66-200 Świebodzin</t>
+          <t>Floriańska 180, 31-019 Kraków</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>66-200</t>
+          <t>31-019</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18249,12 +18249,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>17/07/2022</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -18351,17 +18351,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5299D83YTOJE94ZUPK91</t>
+          <t>6299D83YTOJE94ZUPK91</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Silesia Invest S.A.</t>
+          <t>Niebieski Sokół S.A.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ul. Armii Krajowej 17/45, 78-100 Kołobrzeg</t>
+          <t>ul. Długa 17/45, 31-147 Kraków</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18371,7 +18371,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>78-100</t>
+          <t>31-147</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -18391,12 +18391,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>2023/24/08</t>
+          <t>2023/19/03</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -18498,12 +18498,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Vistula Fintech SA</t>
+          <t>Niebieski Orzeł SA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 34, 73-110 Stargard</t>
+          <t>ul Piotrkowska 34, 90-102 Łódź</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>73-110</t>
+          <t>90-102</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>03-09-2024</t>
+          <t>26-04-2024</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -18640,12 +18640,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Astra Finance S. A.</t>
+          <t>Niebieski Kormoran S. A.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ulica Mickiewicza 51, 27-600 Sandomierz</t>
+          <t>ulica Zachodnia 51, 90-402 Łódź</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>27-600</t>
+          <t>90-402</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -18675,12 +18675,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -18782,12 +18782,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka Akcyjna</t>
+          <t>Niebieski Barycz Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Sienkiewicza 68, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>Świdnicka 68, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -18797,7 +18797,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>27-400</t>
+          <t>50-066</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -18817,12 +18817,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>20261117</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -18924,12 +18924,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o.o.</t>
+          <t>Niebieski Noteć sp. z o.o.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ul. Marszałkowska 85/7, 00-590 Warszawa</t>
+          <t>ul. Legnicka 85/7, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18939,7 +18939,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>00-590</t>
+          <t>54-203</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>24/12/2015</t>
+          <t>19/07/2015</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
+          <t>2015-08-04</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
@@ -19066,12 +19066,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp z oo</t>
+          <t>Niebieski Pilica sp z oo</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 102, 00-071 Warszawa</t>
+          <t>ul Święty Marcin 102, 61-806 Poznań</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19081,7 +19081,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>00-071</t>
+          <t>61-806</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -19101,12 +19101,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>2016/03/01</t>
+          <t>2016/26/08</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -19136,7 +19136,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>245575305</t>
+          <t>255496147</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -19208,12 +19208,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o. o.</t>
+          <t>Niebieski Narew sp. z o. o.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ulica Floriańska 119, 31-019 Kraków</t>
+          <t>ulica Głogowska 119, 60-734 Poznań</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19223,7 +19223,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>31-019</t>
+          <t>60-734</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -19243,17 +19243,17 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>10-02-2017</t>
+          <t>05-09-2017</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2017-01-05</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -19350,12 +19350,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Optima Trade Sp. z o.o.</t>
+          <t>Niebieski Jodełka Sp. z o.o.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Długa 136, 31-147 Kraków</t>
+          <t>Długa 136, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>31-147</t>
+          <t>80-831</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -19385,12 +19385,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>2018-17-03</t>
+          <t>2018-12-10</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>6299QSUWY02468ACEG83</t>
+          <t>5299QSUWY02468ACEG83</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
@@ -19492,12 +19492,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Niebieski Kaktus SP Z O O</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 153/59, 90-102 Łódź</t>
+          <t>ul. Grunwaldzka 153/59, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19507,7 +19507,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>90-102</t>
+          <t>80-236</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -19527,12 +19527,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>20190424</t>
+          <t>20191119</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -19634,12 +19634,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Quantum Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Szmaragd spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>80-236 Gdańsk</t>
+          <t>21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>80-236</t>
+          <t>21-500</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -19669,12 +19669,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>03/05/2020</t>
+          <t>26/12/2020</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -19704,7 +19704,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>245892069</t>
+          <t>255812909</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-01-11</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
@@ -19776,12 +19776,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Topaz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 7, 50-066 Wrocław</t>
+          <t>ulica Wyszyńskiego 7, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>50-066</t>
+          <t>70-200</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -19811,12 +19811,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>2021/10/06</t>
+          <t>2021/05/01</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -19918,12 +19918,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Niebieski Granit S.A.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Legnicka 24, 54-203 Wrocław</t>
+          <t>Mariacka 24, 40-014 Katowice</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>54-203</t>
+          <t>40-014</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -19953,17 +19953,17 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>17-07-2022</t>
+          <t>12-02-2022</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -20060,12 +20060,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>P.P.H.U. Astra Finance</t>
+          <t>P.P.H.U. Niebieski Marmur</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 41/21, 61-806 Poznań</t>
+          <t>ul. Warszawska 41/21, 40-009 Katowice</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20075,7 +20075,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>61-806</t>
+          <t>40-009</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -20095,12 +20095,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>2023-24-08</t>
+          <t>2023-19-03</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -20202,12 +20202,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S. A.</t>
+          <t>Niebieski Syrena S. A.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ul Głogowska 58, 60-734 Poznań</t>
+          <t>ul Krakowskie Przedmieście 58, 20-002 Lublin</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20217,7 +20217,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>60-734</t>
+          <t>20-002</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -20237,12 +20237,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>20240903</t>
+          <t>20240426</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -20344,12 +20344,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka Akcyjna</t>
+          <t>Niebieski Zodiak Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ulica Długa 75, 80-831 Gdańsk</t>
+          <t>ulica Narutowicza 75, 20-004 Lublin</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -20359,7 +20359,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>80-831</t>
+          <t>20-004</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -20379,12 +20379,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -20486,12 +20486,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o.o.</t>
+          <t>Niebieski Olimp sp. z o.o.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Grunwaldzka 92, 80-236 Gdańsk</t>
+          <t>Lipowa 92, 15-424 Białystok</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -20501,7 +20501,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>80-236</t>
+          <t>15-424</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -20521,12 +20521,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>2026/17/11</t>
+          <t>2026/12/06</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -20611,7 +20611,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
@@ -20628,12 +20628,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Niebieski Zorza sp z oo</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 109/73, 70-435 Szczecin</t>
+          <t>ul. Sienkiewicza 109/73, 15-092 Białystok</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -20643,7 +20643,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>70-435</t>
+          <t>15-092</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -20663,12 +20663,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>24-12-2015</t>
+          <t>19-07-2015</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -20770,12 +20770,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o. o.</t>
+          <t>Niebieski Krokus sp. z o. o.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>os. Wyszyńskiego 126, 70-200 Szczecin</t>
+          <t>os. Gdańska 126, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -20785,7 +20785,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>70-200</t>
+          <t>85-005</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -20805,12 +20805,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-26-08</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -20912,12 +20912,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Polaris Capital Sp. z o.o.</t>
+          <t>Niebieski Narcyz Sp. z o.o.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ulica Mariacka 143, 40-014 Katowice</t>
+          <t>ulica Dworcowa 143, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>40-014</t>
+          <t>85-009</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -20947,12 +20947,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>20170210</t>
+          <t>20170905</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Quantum Services SP Z O O</t>
+          <t>Niebieski Giewont SP Z O O</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Warszawska 160, 40-009 Katowice</t>
+          <t>Szeroka 160, 87-100 Toruń</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -21069,7 +21069,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>40-009</t>
+          <t>87-100</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -21089,12 +21089,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>17/03/2018</t>
+          <t>12/10/2018</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -21196,12 +21196,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Silesia Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 177/35, 20-002 Lublin</t>
+          <t>ul. Chełmińska 177/35, 87-100 Toruń</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -21211,7 +21211,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>20-002</t>
+          <t>87-100</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -21231,12 +21231,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>2019/24/04</t>
+          <t>2019/19/11</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -21321,7 +21321,7 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2019-08-04</t>
+          <t>2019-04-08</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
@@ -21338,12 +21338,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Kasprowy Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ul Narutowicza 14, 20-004 Lublin</t>
+          <t>ul 3 Maja 14, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -21353,7 +21353,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>20-004</t>
+          <t>35-030</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -21373,12 +21373,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>03-05-2020</t>
+          <t>26-12-2020</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -21480,12 +21480,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Astra Finance S.A.</t>
+          <t>Amber Budownictwo S.A.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ulica Lipowa 31, 15-424 Białystok</t>
+          <t>ulica Piłsudskiego 31, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -21495,7 +21495,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>15-424</t>
+          <t>35-074</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -21515,22 +21515,22 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>2021-05-01</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>20210901</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>02/10/2021</t>
+          <t/>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -21622,12 +21622,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SA</t>
+          <t>Amber Transport SA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Sienkiewicza 48, 15-092 Białystok</t>
+          <t>Sienkiewicza 48, 25-007 Kielce</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -21637,7 +21637,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>15-092</t>
+          <t>25-007</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -21657,12 +21657,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>20220717</t>
+          <t>20220212</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -21692,7 +21692,7 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>246921531</t>
+          <t>346921531</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
@@ -21759,17 +21759,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>62991K3M5O7Q9SBUDW28</t>
+          <t>52991K3M5O7Q9SBUDW28</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Helios Markets S. A.</t>
+          <t>Amber Spedycja S. A.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ul. Gdańska 65/87, 85-005 Bydgoszcz</t>
+          <t>ul. Warszawska 65/87, 25-512 Kielce</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -21779,7 +21779,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>85-005</t>
+          <t>25-512</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>24/08/2023</t>
+          <t>19/03/2023</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -21906,12 +21906,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>Amber Logistyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ul Dworcowa 82, 85-009 Bydgoszcz</t>
+          <t>ul Kościuszki 82, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -21921,7 +21921,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>85-009</t>
+          <t>10-504</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -21941,12 +21941,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>03/09/2024 08:14</t>
+          <t>26/04/2024 08:14</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -22048,12 +22048,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o.o.</t>
+          <t>Amber Handel sp. z o.o.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ulica Szeroka 99, 87-100 Toruń</t>
+          <t>ulica Dąbrowszczaków 99, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -22063,7 +22063,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>87-100</t>
+          <t>10-540</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -22083,12 +22083,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>10-10-2025</t>
+          <t>05-05-2025</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -22190,12 +22190,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Amber Usługi sp z oo</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Chełmińska 116, 87-100 Toruń</t>
+          <t>Krakowska 116, 45-018 Opole</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -22205,7 +22205,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>87-100</t>
+          <t>45-018</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -22225,12 +22225,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>2026-17-11</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -22332,12 +22332,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o. o.</t>
+          <t>Amber Finanse sp. z o. o.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 133/49, 35-030 Rzeszów</t>
+          <t>ul. Ozimska 133/49, 45-057 Opole</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -22347,7 +22347,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>35-030</t>
+          <t>45-057</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -22367,12 +22367,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>20151224</t>
+          <t>20150719</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -22474,12 +22474,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Quantum Services Sp. z o.o.</t>
+          <t>Amber Doradztwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 150, 35-074 Rzeszów</t>
+          <t>ul Bohaterów Westerplatte 150, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -22489,7 +22489,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>35-074</t>
+          <t>65-034</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -22504,17 +22504,17 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>sp. z o.o.</t>
+          <t>s. z o.o.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>03/01/2016</t>
+          <t>26/08/2016</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -22529,7 +22529,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>529900T8BM49AURSDO55</t>
+          <t>529900T8B49UARSDO55</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -22564,7 +22564,7 @@
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>ACITVE</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="U159" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>2016-11-09</t>
+          <t>2016-09-11</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
@@ -22616,12 +22616,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Amber Szkolenia SP Z O O</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 167, 25-007 Kielce</t>
+          <t>ulica Kupiecka 167, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>25-007</t>
+          <t>65-058</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -22651,12 +22651,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>2017/10/02</t>
+          <t>2017/05/09</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -22666,7 +22666,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2017-02-06</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -22758,12 +22758,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Vistula Fintech spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Media spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Warszawska 4, 25-512 Kielce</t>
+          <t>Świętojańska 4, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -22773,7 +22773,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>25-512</t>
+          <t>81-372</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -22793,17 +22793,17 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>17-03-2018</t>
+          <t>12-10-2018</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -22905,7 +22905,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 21/11, 10-504 Olsztyn</t>
+          <t>ul. 10 Lutego 21/11, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -22915,7 +22915,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>10-504</t>
+          <t>81-364</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -22935,12 +22935,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>2019-24-04</t>
+          <t>2019-19-11</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-02-06</t>
         </is>
       </c>
       <c r="V162" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-02-06</t>
         </is>
       </c>
     </row>
@@ -23042,12 +23042,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Amber Marketing S.A.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ul Dąbrowszczaków 38, 10-540 Olsztyn</t>
+          <t>ul Bolesława Prusa 38, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -23057,7 +23057,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>10-540</t>
+          <t>05-800</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -23077,12 +23077,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>20200503</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -23112,7 +23112,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>347713438</t>
+          <t>247713438</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
@@ -23184,12 +23184,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Helios Markets SA</t>
+          <t>Amber Druk SA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ulica Krakowska 55, 45-018 Opole</t>
+          <t>ulica Kościuszki 55, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>45-018</t>
+          <t>05-500</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -23219,12 +23219,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>10/06/2021</t>
+          <t>05/01/2021</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -23326,12 +23326,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Lumen Advisory S. A.</t>
+          <t>Amber Informatyka S. A.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ozimska 72, 45-057 Opole</t>
+          <t>Sienkiewicza 72, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>45-057</t>
+          <t>32-020</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -23361,12 +23361,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>2022/17/07</t>
+          <t>2022/12/02</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -23376,7 +23376,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -23451,7 +23451,7 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2022-01-07</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
@@ -23468,12 +23468,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Amber Oprogramowanie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Westerplatte 89/63, 65-034 Zielona Góra</t>
+          <t>ul. Dąbrowskiego 89/63, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -23483,7 +23483,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>65-034</t>
+          <t>32-600</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -23503,12 +23503,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>24-08-2023</t>
+          <t>19-03-2023</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -23610,12 +23610,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o.o.</t>
+          <t>Amber Rolnictwo sp. z o.o.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ul Kupiecka 106, 65-058 Zielona Góra</t>
+          <t>ul Rynek 106, 38-400 Krosno</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -23625,7 +23625,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>65-058</t>
+          <t>38-400</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -23645,12 +23645,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-26-04</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -23752,12 +23752,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Amber Ogrodnictwo sp z oo</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ulica Świętojańska 123, 81-372 Gdynia</t>
+          <t>ulica Mickiewicza 123, 39-300 Mielec</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -23767,7 +23767,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>81-372</t>
+          <t>39-300</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -23787,12 +23787,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>20251010</t>
+          <t>20250505</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -23894,12 +23894,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o. o.</t>
+          <t>Amber Produkcja sp. z o. o.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>10 Lutego 140, 81-364 Gdynia</t>
+          <t>Długa 140, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -23909,7 +23909,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>81-364</t>
+          <t>58-100</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -23929,12 +23929,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>17/11/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -24036,12 +24036,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Silesia Invest Sp. z o.o.</t>
+          <t>Amber Przemysł Sp. z o.o.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ul. Bolesława Prusa 157/25, 05-800 Pruszków</t>
+          <t>157/25, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -24051,7 +24051,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>05-800</t>
+          <t>57-300</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -24071,12 +24071,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>2015/24/12</t>
+          <t>2015/19/07</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>6299543210ZYXWVUTS73</t>
+          <t>5299543210ZYXWVUTS73</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -24161,7 +24161,7 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
+          <t>2015-12-08</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
@@ -24178,12 +24178,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Vistula Fintech SP Z O O</t>
+          <t>Amber Ekologia SP Z O O</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ul Kościuszki 174, 05-500 Piaseczno</t>
+          <t>ul Chrobrego 174, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -24193,7 +24193,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>05-500</t>
+          <t>62-200</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -24213,12 +24213,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>03-01-2016</t>
+          <t>26-08-2016</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -24320,12 +24320,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Astra Finance spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Energetyka spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 11, 32-020 Wieliczka</t>
+          <t>ulica Słowiańska 11, 64-100 Leszno</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -24335,7 +24335,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>32-020</t>
+          <t>64-100</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -24355,12 +24355,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>2017-10-02</t>
+          <t>2017-05-09</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -24462,12 +24462,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Instalacje Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Dąbrowskiego 28, 32-600 Oświęcim</t>
+          <t>Gdańska 28, 83-110 Tczew</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -24477,7 +24477,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>32-600</t>
+          <t>83-110</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -24497,12 +24497,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>20180317</t>
+          <t>20181012</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -24604,12 +24604,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Amber Nieruchomości S.A.</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>ul. Rynek 45/77, 38-400 Krosno</t>
+          <t>ul. Sobieskiego 45/77, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -24619,7 +24619,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>38-400</t>
+          <t>84-200</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -24639,12 +24639,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>24/04/2019</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -24704,7 +24704,7 @@
       </c>
       <c r="V174" t="inlineStr">
         <is>
-          <t>2019-04-12</t>
+          <t>2019-12-04</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
@@ -24746,12 +24746,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Lumen Advisory SA</t>
+          <t>Amber Inwestycje SA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 62, 39-300 Mielec</t>
+          <t>ul Głęboka 62, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -24761,7 +24761,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>39-300</t>
+          <t>43-400</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -24781,12 +24781,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2020/03/05</t>
+          <t>2020/26/12</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -24888,12 +24888,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Nova Data S. A.</t>
+          <t>Amber Medycyna S. A.</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>os. Długa 79, 58-100 Świdnica</t>
+          <t>os. Małachowskiego 79, 42-500 Będzin</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -24903,7 +24903,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>58-100</t>
+          <t>42-500</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -24923,17 +24923,17 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>10-06-2021</t>
+          <t>05-01-2021</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2021-01-09</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -25030,12 +25030,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Amber Zdrowie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>96, 57-300 Kłodzko</t>
+          <t>Królowej Jadwigi 96, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -25045,7 +25045,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>57-300</t>
+          <t>88-100</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -25065,12 +25065,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2022-17-07</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -25172,12 +25172,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Amber Urody sp. z o.o.</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ul. Chrobrego 113/39, 62-200 Gniezno</t>
+          <t>ul. Wybickiego 113/39, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -25187,7 +25187,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>62-200</t>
+          <t>86-300</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -25207,12 +25207,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>20230824</t>
+          <t>20230319</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -25314,12 +25314,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Amber Turystyka sp z oo</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ul Słowiańska 130, 64-100 Leszno</t>
+          <t>ul Czarnieckiego 130, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>64-100</t>
+          <t>14-100</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -25349,12 +25349,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>03/09/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -25414,7 +25414,7 @@
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
@@ -25456,12 +25456,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o. o.</t>
+          <t>Amber Rozrywka sp. z o. o.</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ulica Gdańska 147, 83-110 Tczew</t>
+          <t>ulica Warszawska 147, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>83-110</t>
+          <t>11-500</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -25491,12 +25491,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>2025/10/10</t>
+          <t>2025/05/05</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -25598,12 +25598,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Vistula Fintech Sp. z o.o.</t>
+          <t>Amber Gastronomia Sp. z o.o.</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sobieskiego 164, 84-200 Wejherowo</t>
+          <t>Lubelska 164, 24-100 Puławy</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>84-200</t>
+          <t>24-100</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -25633,17 +25633,17 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>17-11-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -25668,7 +25668,7 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>249218045</t>
+          <t>259138887</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
@@ -25740,12 +25740,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Amber Moda</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ul. Głęboka 1/1, 43-400 Cieszyn</t>
+          <t>ul. Staszica 1/1, 22-400 Zamość</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -25755,7 +25755,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>43-400</t>
+          <t>22-400</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -25775,12 +25775,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>2015-24-12</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -25835,7 +25835,7 @@
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="V182" t="inlineStr">
@@ -25870,7 +25870,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
     </row>
@@ -25882,12 +25882,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Baltic Med Supply spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Tekstylia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ul Małachowskiego 18, 42-500 Będzin</t>
+          <t>ul 3 Maja 18, 16-300 Augustów</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -25897,7 +25897,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>42-500</t>
+          <t>16-300</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -25917,12 +25917,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>20160103</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -26024,12 +26024,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Motoryzacja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ulica Królowej Jadwigi 35, 88-100 Inowrocław</t>
+          <t>ulica Kościuszki 35, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -26039,7 +26039,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>88-100</t>
+          <t>16-400</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -26059,12 +26059,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>10/02/2017</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -26166,12 +26166,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Amber Ubezpieczenia S.A.</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>os. Kościuszki 172, 16-400</t>
+          <t>os. Kupiecka 172, 65-058</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -26181,7 +26181,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>16-400</t>
+          <t>65-058</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -26201,12 +26201,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>2018/17/03</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -26216,7 +26216,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2018-01-03</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr">
@@ -26308,12 +26308,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Nova Data SA</t>
+          <t>Amber Spawalnictwo SA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>ul. Czarnieckiego 69/53, 14-100 Ostróda</t>
+          <t>ul. Długa 69/53, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -26323,7 +26323,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>14-100</t>
+          <t>49-300</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -26343,12 +26343,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>24-04-2019</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>62999O3IXCR6L0FU9O92</t>
+          <t>52999O3IXCR6L0FU9O92</t>
         </is>
       </c>
       <c r="X186" t="inlineStr">
@@ -26450,12 +26450,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Optima Trade S. A.</t>
+          <t>Amber Ślusarstwo S. A.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ul Warszawska 86, 11-500 Giżycko</t>
+          <t>ul Rynek 86, 68-200 Żary</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -26465,7 +26465,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>11-500</t>
+          <t>68-200</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -26485,12 +26485,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-26-12</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -26592,12 +26592,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka Akcyjna</t>
+          <t>Amber Krawiectwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ulica Lubelska 103, 24-100 Puławy</t>
+          <t>ulica Sikorskiego 103, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -26607,7 +26607,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>24-100</t>
+          <t>66-200</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -26627,12 +26627,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>20210610</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -26734,12 +26734,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Amber Ochrona sp. z o.o.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Staszica 120, 22-400 Zamość</t>
+          <t>Armii Krajowej 120, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -26749,7 +26749,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>22-400</t>
+          <t>78-100</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -26769,12 +26769,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>17/07/2022</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -26876,12 +26876,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Amber Catering sp z oo</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 137/15, 16-300 Augustów</t>
+          <t>ul. Piłsudskiego 137/15, 73-110 Stargard</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -26891,7 +26891,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>16-300</t>
+          <t>73-110</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -26911,12 +26911,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>2023/24/08</t>
+          <t>2023/19/03</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -27018,12 +27018,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o. o.</t>
+          <t>Amber Księgowość sp. z o. o.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ul Kościuszki 154, 16-400 Suwałki</t>
+          <t>154, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -27033,7 +27033,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>16-400</t>
+          <t>27-600</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -27053,12 +27053,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>03-09-2024</t>
+          <t>26-04-2024</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>250009941</t>
+          <t>259930787</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
@@ -27160,12 +27160,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Astra Finance Sp. z o.o.</t>
+          <t>Bizon Budownictwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ulica Piastowska 171, 48-300 Nysa</t>
+          <t>ulica Sienkiewicza 171, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -27175,7 +27175,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>48-300</t>
+          <t>27-400</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -27195,12 +27195,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -27302,12 +27302,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Bizon Transport SP Z O O</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Długa 8, 49-300 Brzeg</t>
+          <t>Chmielna 8, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -27317,7 +27317,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>49-300</t>
+          <t>00-020</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -27337,12 +27337,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>20261117</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -27444,12 +27444,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Spedycja spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ul. Rynek 25/67, 68-200 Żary</t>
+          <t>ul. Nowy Świat 25/67, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -27459,7 +27459,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>68-200</t>
+          <t>00-029</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -27479,12 +27479,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>24/12/2015</t>
+          <t>19/07/2015</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -27544,7 +27544,7 @@
       </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
+          <t>2015-08-04</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
@@ -27586,12 +27586,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Logistyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ul Sikorskiego 42, 66-200 Świebodzin</t>
+          <t>ul os. Przyjaźń 42, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -27601,7 +27601,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>66-200</t>
+          <t>01-355</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -27621,12 +27621,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>2016/03/01</t>
+          <t>2016/26/08</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -27728,12 +27728,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Nova Data S.A.</t>
+          <t>Bizon Handel S.A.</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ulica Armii Krajowej 59, 78-100 Kołobrzeg</t>
+          <t>ulica Jagiellońska 59, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -27743,7 +27743,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>78-100</t>
+          <t>05-120</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -27763,17 +27763,17 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>10-02-2017</t>
+          <t>05-09-2017</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2017-01-05</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -27833,7 +27833,7 @@
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>52997WLAZOD2RG5UJ835</t>
+          <t>62997WLAZOD2RG5UJ835</t>
         </is>
       </c>
       <c r="X196" t="inlineStr">
@@ -27870,12 +27870,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Optima Trade SA</t>
+          <t>Bizon Usługi SA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Piłsudskiego 76, 73-110 Stargard</t>
+          <t>Piłsudskiego 76, 05-270 Marki</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>73-110</t>
+          <t>05-270</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -27905,12 +27905,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>2018-17-03</t>
+          <t>2018-12-10</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -28012,12 +28012,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Polaris Capital S. A.</t>
+          <t>Bizon Finanse S. A.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>93/29, 27-600 Sandomierz</t>
+          <t>ul. Andriollego 93/29, 05-400 Otwock</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -28027,7 +28027,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>27-600</t>
+          <t>05-400</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -28047,12 +28047,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>20190424</t>
+          <t>20191119</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -28154,12 +28154,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka Akcyjna</t>
+          <t>Bizon Doradztwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 110, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>ul Żeromskiego 110, 26-600 Radom</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -28169,7 +28169,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>27-400</t>
+          <t>26-600</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -28189,12 +28189,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>03/05/2020</t>
+          <t>26/12/2020</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -28254,7 +28254,7 @@
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-01-11</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
@@ -28296,12 +28296,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Bizon Szkolenia sp. z o.o.</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 127, 00-590 Warszawa</t>
+          <t>ulica Tumska 127, 09-402 Płock</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -28311,7 +28311,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>00-590</t>
+          <t>09-402</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -28331,12 +28331,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>2021/10/06</t>
+          <t>2021/05/01</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -28438,12 +28438,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Bizon Media sp z oo</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 144, 00-071 Warszawa</t>
+          <t>Karmelicka 144, 31-128 Kraków</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -28453,7 +28453,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>00-071</t>
+          <t>31-128</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -28473,17 +28473,17 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>17-07-2022</t>
+          <t>12-02-2022</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">

--- a/data/xlsx/gleif.xlsx
+++ b/data/xlsx/gleif.xlsx
@@ -21520,7 +21520,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t/>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -21535,7 +21535,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>529900T8BM49AURSDO55</t>
+          <t/>
         </is>
       </c>
       <c r="N152" t="inlineStr">

--- a/data/xlsx/gleif.xlsx
+++ b/data/xlsx/gleif.xlsx
@@ -215,12 +215,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2015-24-12</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -275,7 +275,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -310,7 +310,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
     </row>
@@ -322,7 +322,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Polskie Przetwory sp z oo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -357,12 +357,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20160103</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -464,7 +464,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o. o.</t>
+          <t>Hurtownia Nabiału Mleczko sp. z o. o.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -499,12 +499,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10/02/2017</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lumen Advisory Sp. z o.o.</t>
+          <t>Agencja Reklamowa Kreatywni Sp. z o.o.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2018/17/03</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-01-03</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nova Data SP Z O O</t>
+          <t>Kancelaria Prawna Sankcja SP Z O O</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24-04-2019</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0000000396</t>
+          <t>000000039</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Śląskie Zakłady Mechaniczne spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-26-12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Fabryka Okien i Drzwi Profil Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20210610</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quantum Services S.A.</t>
+          <t>Przedsiębiorstwo Robót Drogowych S.A.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bydgo</t>
+          <t>Bdygo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17/07/2022</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>529900T8BM49AURSDO55</t>
+          <t>529900T8BM49UARSDO55</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>IS_DIRECTLY_CONSOLIDATED_BY</t>
+          <t>IS_DIRECLTY_CONSOLIDATED_BY</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Silesia Invest SA</t>
+          <t>Krakowskie Biuro Nieruchomości SA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2023/24/08</t>
+          <t>2023/19/03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vistula Fintech S. A.</t>
+          <t>Salon Samochodowy Auto-Hit S. A.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>03-09-2024</t>
+          <t>26-04-2024</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka Akcyjna</t>
+          <t>Klinika Stomatologiczna Dent-Med Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1635,12 +1635,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1737,12 +1737,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6299M8UG2OAWI4QCYK86</t>
+          <t>5299M8UG2OAWI4QCYK86</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Polski Tytoń sp. z o.o.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>20261117</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>335834938</t>
+          <t>235834938</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Gdańska Stocznia Jachtowa sp z oo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>24/12/2015</t>
+          <t>19/07/2015</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
+          <t>2015-08-04</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o. o.</t>
+          <t>Wytwórnia Makaronu Jajecznego sp. z o. o.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2016/03/01</t>
+          <t>2016/26/08</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nova Data Sp. z o.o.</t>
+          <t>Zakłady Mięsne Tradycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2203,17 +2203,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>10-02-2017</t>
+          <t>05-09-2017</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2017-01-05</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optima Trade SP Z O O</t>
+          <t>Spółdzielnia Mleczarska Radomsko SP Z O O</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2345,12 +2345,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2018-17-03</t>
+          <t>2018-12-10</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Polaris Capital spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kancelaria Finansowo-Księgowa Bilans spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20190424</t>
+          <t>20191119</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zarząd Nieruchomości Komercyjnych Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2629,64 +2629,64 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>26/12/2020</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2020/22/08</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>23-09-2020</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>03/05/2020</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2020/22/08</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>23-09-2020</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>National Official Business Register (Central Statistical Office) | Krajowy Rejestr Urzedowy Podmiotow Gospodarki Narodowej REGON (Glowny Urzad Statystyczny) | Poland | RA000484</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>236310077</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>5299SKC4WOG80SKC4W71</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>National Official Business Register (Central Statistical Office) | Krajowy Rejestr Urzedowy Podmiotow Gospodarki Narodowej REGON (Glowny Urzad Statystyczny) | Poland | RA000484</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>236310077</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>5299SKC4WOG80SKC4W71</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>13/03/2020</t>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-01-11</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Silesia Invest S.A.</t>
+          <t>Polskie Linie Oceaniczne S.A.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2021/10/06</t>
+          <t>2021/05/01</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vistula Fintech SA</t>
+          <t>Hurtownia Materiałów Budowlanych Cegiełka SA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Piłsudskiego 84, Rzeszów</t>
+          <t>Rynek 84, Opole</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>17-07-2022</t>
+          <t>12-02-2022</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Studio Projektowe Architektura</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2023-24-08</t>
+          <t>2023-19-03</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka Akcyjna</t>
+          <t>Centrum Medycyny Pracy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>20240903</t>
+          <t>20240426</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o.o.</t>
+          <t>Przedsiębiorstwo Energetyki Cieplnej sp. z o.o.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3339,12 +3339,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp z oo</t>
+          <t>Gospodarstwo Rolno-Ogrodnicze sp z oo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026/17/11</t>
+          <t>2026/12/06</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o. o.</t>
+          <t>Drukarnia Wielkoformatowa Impress sp. z o. o.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>24-12-2015</t>
+          <t>19-07-2015</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optima Trade Sp. z o.o.</t>
+          <t>Klub Fitness Sylwetka Sp. z o.o.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-26-08</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Polska Grupa Energetyczna SP Z O O</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>20170210</t>
+          <t>20170905</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Quantum Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Mazowieckie Zakłady Drobiarskie spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>17/03/2018</t>
+          <t>12/10/2018</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6299QSUWY02468ACEG83</t>
+          <t>5299QSUWY02468ACEG83</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Hurtownia Farmaceutyczna Aptekarz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2019/24/04</t>
+          <t>2019/19/11</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2019-08-04</t>
+          <t>2019-04-08</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Kancelaria Notarialna Lex S.A.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>03-05-2020</t>
+          <t>26-12-2020</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Astra Finance SA</t>
+          <t>Biuro Podróży Wojażer SA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4475,12 +4475,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S. A.</t>
+          <t>Szkoła Języków Obcych Lingua S. A.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>20220717</t>
+          <t>20220212</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka Akcyjna</t>
+          <t>Centrum Logistyczne Podlasie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>24/08/2023</t>
+          <t>19/03/2023</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o.o.</t>
+          <t>Fabryka Mebli Drewnianych Dąb sp. z o.o.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2024/03/09</t>
+          <t>2024/26/04</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Polskie Sady sp z oo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>10-10-2025</t>
+          <t>05-05-2025</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o. o.</t>
+          <t>Wielkopolska Hurtownia Stali sp. z o. o.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-17-11</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Polaris Capital Sp. z o.o.</t>
+          <t>Zakład Oczyszczania Miasta Sp. z o.o.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>20151224</t>
+          <t>20150719</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Quantum Services SP Z O O</t>
+          <t>Przedsiębiorstwo Wodociągów i Kanalizacji SP Z O O</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>57-300 Kłodzko</t>
+          <t>70-435 Szczecin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>57-300</t>
+          <t>70-435</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>03/01/2016</t>
+          <t>26/08/2016</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2016-11-09</t>
+          <t>2016-09-11</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Silesia Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Instytut Badań Rynkowych spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2017/10/02</t>
+          <t>2017/05/09</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2017-02-06</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Agencja Ochrony Solidna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5753,17 +5753,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>17-03-2018</t>
+          <t>12-10-2018</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2019-24-04</t>
+          <t>2019-19-11</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-02-06</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-02-06</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SA</t>
+          <t>Krajowa Izba Gospodarcza SA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>20200503</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Helios Markets S. A.</t>
+          <t>Polskie Zakłady Lotnicze S. A.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>10/06/2021</t>
+          <t>05/01/2021</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>Hurtownia Elektryczna Wat Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2022/17/07</t>
+          <t>2022/12/02</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>6299UCUCUCUCUCUCUC27</t>
+          <t>5299UCUCUCUCUCUCUC27</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-01-07</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o.o.</t>
+          <t>Centrum Ogrodnicze Zielona Oaza sp. z o.o.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>24-08-2023</t>
+          <t>19-03-2023</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Piekarnia i Cukiernia Chrupiący Rogalik sp z oo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-26-04</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o. o.</t>
+          <t>Zakład Usług Komunalnych sp. z o. o.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>20251010</t>
+          <t>20250505</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Quantum Services Sp. z o.o.</t>
+          <t>Polski Komfort Sp. z o.o.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>17/11/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Kancelaria Radców Prawnych Partnerzy SP Z O O</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2015/24/12</t>
+          <t>2015/19/07</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
+          <t>2015-12-08</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vistula Fintech spółka z ograniczoną odpowiedzialnością</t>
+          <t>Centrum Dystrybucji Alkoholi spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>03-01-2016</t>
+          <t>26-08-2016</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Przedsiębiorstwo Spedycyjne Ładunek Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2017-10-02</t>
+          <t>2017-05-09</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Fabryka Tekstyliów Splot S.A.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>20180317</t>
+          <t>20181012</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Helios Markets SA</t>
+          <t>Górnośląskie Towarzystwo Finansowe SA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>24/04/2019</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2019-04-12</t>
+          <t>2019-12-04</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Lumen Advisory S. A.</t>
+          <t>Krajowa Agencja Informacyjna S. A.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2020/03/05</t>
+          <t>2020/26/12</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>239160916</t>
+          <t>339160916</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Polskie Jagody Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7883,17 +7883,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>10-06-2021</t>
+          <t>05-01-2021</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2021-01-09</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o.o.</t>
+          <t>Zielony Amber sp. z o.o.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2022-17-07</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Zielony Bizon sp z oo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8167,12 +8167,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2023-08-24T07:55:39Z</t>
+          <t>2023-03-19T07:55:39Z</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o. o.</t>
+          <t>Zielnoy Canyon sp. z o. o.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>03/09/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>PARTIALL_CORROBORATED</t>
+          <t>PRATIALL_CORROBORATED</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>ACTVIE</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>IS_ULTIMATELY_CONSLOIADTED_BY</t>
+          <t>IS_ULTIMATELY_CONSLOIDATED_BY</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Silesia Invest Sp. z o.o.</t>
+          <t>Zielony Delfin Sp. z o.o.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2025/10/10</t>
+          <t>2025/05/05</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Vistula Fintech SP Z O O</t>
+          <t>Zielony Echo SP Z O O</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8593,17 +8593,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>17-11-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -8695,12 +8695,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6299543210ZYXWVUTS73</t>
+          <t>5299543210ZYXWVUTS73</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>P.P.H.U. Astra Finance</t>
+          <t>P.P.H.U. Zielony Falcon</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2015-24-12</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Gryf Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>20160103</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>339794437</t>
+          <t>239794437</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>5299CCCCCCCCCCCCCC47</t>
+          <t>6299CCCCCCCCCCCCCC47</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Zielony Horyzont S.A.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>10/02/2017</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lumen Advisory SA</t>
+          <t>Zielony Ikar SA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2018/17/03</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2018-01-03</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nova Data S. A.</t>
+          <t>Zielony Jantar S. A.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9303,12 +9303,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>24-04-2019</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Zielony Koral Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-26-12</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Zielony Lotos sp. z o.o.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 43, 00-590 Warszawa</t>
+          <t>ulica Chmielna 43, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>00-590</t>
+          <t>00-020</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>20210610</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -9694,12 +9694,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Zielony Magnolia sp z oo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 60, 00-071 Warszawa</t>
+          <t>Nowy Świat 60, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>00-071</t>
+          <t>00-029</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -9729,12 +9729,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>17/07/2022</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -9836,12 +9836,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o. o.</t>
+          <t>Zielony Neon sp. z o. o.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ul. Floriańska 77/75, 31-019 Kraków</t>
+          <t>ul. os. Przyjaźń 77/75, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>31-019</t>
+          <t>01-355</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2023/24/08</t>
+          <t>2023/19/03</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Vistula Fintech Sp. z o.o.</t>
+          <t>Zielony Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ul Długa 94, 31-147 Kraków</t>
+          <t>ul Jagiellońska 94, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>31-147</t>
+          <t>05-120</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>03-09-2024</t>
+          <t>26-04-2024</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -10120,12 +10120,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Astra Finance SP Z O O</t>
+          <t>Zielony Pegaz SP Z O O</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ulica Piotrkowska 111, 90-102 Łódź</t>
+          <t>ulica Piłsudskiego 111, 05-270 Marki</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>90-102</t>
+          <t>05-270</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -10155,12 +10155,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -10262,12 +10262,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Baltic Med Supply spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Zachodnia 128, 90-402 Łódź</t>
+          <t>Andriollego 128, 05-400 Otwock</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>90-402</t>
+          <t>05-400</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -10297,12 +10297,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>20261117</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Szafir Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ul. Świdnicka 145/37, 50-066 Wrocław</t>
+          <t>ul. Żeromskiego 145/37, 26-600 Radom</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>50-066</t>
+          <t>26-600</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -10439,12 +10439,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>24/12/2015</t>
+          <t>19/07/2015</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
+          <t>2015-08-04</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Zielony Tytan S.A.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ul Legnicka 162, 54-203 Wrocław</t>
+          <t>ul Tumska 162, 09-402 Płock</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>54-203</t>
+          <t>09-402</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2016/03/01</t>
+          <t>2016/26/08</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nova Data SA</t>
+          <t>Zielony Uran SA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ulica Święty Marcin 179, 61-806 Poznań</t>
+          <t>ulica Karmelicka 179, 31-128 Kraków</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>61-806</t>
+          <t>31-128</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -10723,17 +10723,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>10-02-2017</t>
+          <t>05-09-2017</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2017-01-05</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Optima Trade S. A.</t>
+          <t>Zielony Wektor S. A.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Głogowska 16, 60-734 Poznań</t>
+          <t>os. Na Stoku 16, 31-704 Kraków</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>60-734</t>
+          <t>31-704</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2018-17-03</t>
+          <t>2018-12-10</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -10972,12 +10972,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka Akcyjna</t>
+          <t>Zielony Zefir Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ul. Długa 33/89, 80-831 Gdańsk</t>
+          <t>ul. Krupówki 33/89, 34-500 Zakopane</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>80-831</t>
+          <t>34-500</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>20190424</t>
+          <t>20191119</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>62999O3IXCR6L0FU9O92</t>
+          <t>52999O3IXCR6L0FU9O92</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Zielony Żubr sp. z o.o.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ul Grunwaldzka 50, 80-236 Gdańsk</t>
+          <t>50, 34-600 Mordarka</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>80-236</t>
+          <t>34-600</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>03/05/2020</t>
+          <t>26/12/2020</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-01-11</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -11256,12 +11256,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Zielony Sokół sp z oo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 67, 70-435 Szczecin</t>
+          <t>ulica Galicyjska 67, 32-087 Zielonki</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>70-435</t>
+          <t>32-087</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -11291,12 +11291,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2021/10/06</t>
+          <t>2021/05/01</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o. o.</t>
+          <t>Zielony Orzeł sp. z o. o.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wyszyńskiego 84, 70-200 Szczecin</t>
+          <t>84, 32-003 Podłęże</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>70-200</t>
+          <t>32-003</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -11433,17 +11433,17 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>17-07-2022</t>
+          <t>12-02-2022</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ul. Mariacka 101/51, 40-014 Katowice</t>
+          <t>ul. Wałowa 101/51, 33-100 Tarnów</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>40-014</t>
+          <t>33-100</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -11575,12 +11575,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2023-24-08</t>
+          <t>2023-19-03</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -11682,12 +11682,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Zielony Barycz SP Z O O</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ul Warszawska 118, 40-009 Katowice</t>
+          <t>ul Narutowicza 118, 90-135 Łódź</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>40-009</t>
+          <t>90-135</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -11717,12 +11717,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>20240903</t>
+          <t>20240426</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>241457425</t>
+          <t>251378267</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Noteć spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ulica Krakowskie Przedmieście 135, 20-002 Lublin</t>
+          <t>ulica os. Retkinia 135, 94-004 Łódź</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20-002</t>
+          <t>94-004</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -11909,52 +11909,52 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
+          <t>IS_DIRECTLY_CONSOLIDATED_BY</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2025-18-06</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>5299F0L6RCXI3O9UF057</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>20/08/2025</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>2025-18-06</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>5299F0L6RCXI3O9UF057</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>IS_ULTIMATELY_CONSOLIDATED_BY</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>22-10-2025</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
         <is>
           <t/>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>IS_ULTIMATELY_CONSOLIDATED_BY</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>22-10-2025</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>20/08/2025</t>
         </is>
       </c>
     </row>
@@ -11966,12 +11966,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Pilica Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chełmińska 92, 87-100</t>
+          <t>Piastowska 92, 48-300</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>87-100</t>
+          <t>48-300</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026/17/11</t>
+          <t>2026/12/06</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
@@ -12108,12 +12108,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nova Data S.A.</t>
+          <t>Zielony Narew S.A.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ul. Lipowa 169/13, 15-424 Białystok</t>
+          <t>ul. Długa 169/13, 95-100 Zgierz</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>15-424</t>
+          <t>95-100</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>24-12-2015</t>
+          <t>19-07-2015</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -12250,12 +12250,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Optima Trade SA</t>
+          <t>Zielony Jodełka SA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 6, 15-092 Białystok</t>
+          <t>ul Rynek 6, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>15-092</t>
+          <t>50-101</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -12285,12 +12285,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-26-08</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -12392,12 +12392,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Polaris Capital S. A.</t>
+          <t>Zielony Kaktus S. A.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ulica Gdańska 23, 85-005 Bydgoszcz</t>
+          <t>ulica Jedności Narodowej 23, 50-260 Wrocław</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>85-005</t>
+          <t>50-260</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -12427,12 +12427,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>20170210</t>
+          <t>20170905</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka Akcyjna</t>
+          <t>Zielony Szmaragd Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>os. Dworcowa 40, 85-009 Bydgoszcz</t>
+          <t>os. Konstytucji 3 Maja 40, 58-540 Karpacz</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>85-009</t>
+          <t>58-540</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -12569,12 +12569,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>17/03/2018</t>
+          <t>12/10/2018</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -12676,12 +12676,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Zielony Topaz sp. z o.o.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ul. Szeroka 57/65, 87-100 Toruń</t>
+          <t>ul. Odrodzenia 57/65, 59-300 Lubin</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>87-100</t>
+          <t>59-300</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -12711,12 +12711,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2019/24/04</t>
+          <t>2019/19/11</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2019-08-04</t>
+          <t>2019-04-08</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
@@ -12818,12 +12818,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Zielony Granit sp z oo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ul Chełmińska 74, 87-100 Toruń</t>
+          <t>ul Słowackiego 74, 58-300 Wałbrzych</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>87-100</t>
+          <t>58-300</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>03-05-2020</t>
+          <t>26-12-2020</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>242090949</t>
+          <t>252011787</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -12960,12 +12960,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Astra Finance sp. z o. o.</t>
+          <t>Zielony Marmur sp. z o. o.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 91, 35-030 Rzeszów</t>
+          <t>ulica Półwiejska 91, 61-888 Poznań</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>35-030</t>
+          <t>61-888</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -12995,12 +12995,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -13102,12 +13102,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Sp. z o.o.</t>
+          <t>Zielony Syrena Sp. z o.o.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Piłsudskiego 108, 35-074 Rzeszów</t>
+          <t>os. Bolesława Chrobrego 108, 60-681 Poznań</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>35-074</t>
+          <t>60-681</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -13137,12 +13137,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>20220717</t>
+          <t>20220212</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Helios Markets SP Z O O</t>
+          <t>Zielony Zodiak SP Z O O</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 125/27, 25-007 Kielce</t>
+          <t>ul. Główny Rynek 125/27, 62-800 Kalisz</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>25-007</t>
+          <t>62-800</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -13279,12 +13279,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>24/08/2023</t>
+          <t>19/03/2023</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>6299D83YTOJE94ZUPK91</t>
+          <t>5299D83YTOJE94ZUPK91</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Olimp spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ul Warszawska 142, 25-512 Kielce</t>
+          <t>ul Kaliska 142, 63-400 Ostrów Wielkopolski</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>25-512</t>
+          <t>63-400</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -13421,12 +13421,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2024/03/09</t>
+          <t>2024/26/04</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nova Data Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Zorza Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 159, 10-504 Olsztyn</t>
+          <t>ulica Ogarna 159, 80-826 Gdańsk</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>10-504</t>
+          <t>80-826</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>10-10-2025</t>
+          <t>05-05-2025</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -13670,12 +13670,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Optima Trade S.A.</t>
+          <t>Zielony Krokus S.A.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dąbrowszczaków 176, 10-540 Olsztyn</t>
+          <t>os. Jasień 176, 80-180 Gdańsk</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>10-540</t>
+          <t>80-180</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-17-11</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>242566085</t>
+          <t>252486929</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -13812,12 +13812,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Polaris Capital SA</t>
+          <t>Zielony Narcyz SA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ul. Krakowska 13/79, 45-018 Opole</t>
+          <t>ul. Bohaterów Monte Cassino 13/79, 81-759 Sopot</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>45-018</t>
+          <t>81-759</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -13847,12 +13847,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>20151224</t>
+          <t>20150719</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Quantum Services S. A.</t>
+          <t>Zielony Giewont S. A.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ul Ozimska 30, 45-057 Opole</t>
+          <t>30, 80-209 Chwaszczyno</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>45-057</t>
+          <t>80-209</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -13989,12 +13989,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>03/01/2016</t>
+          <t>26/08/2016</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2016-11-09</t>
+          <t>2016-09-11</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
@@ -14096,12 +14096,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka Akcyjna</t>
+          <t>Zielony Rysy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ulica Bohaterów Westerplatte 47, 65-034 Zielona Góra</t>
+          <t>ulica 3 Maja 47, 40-096 Katowice</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>65-034</t>
+          <t>40-096</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -14131,12 +14131,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2017/10/02</t>
+          <t>2017/05/09</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2017-02-06</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -14238,12 +14238,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o.o.</t>
+          <t>Zielony Kasprowy sp. z o.o.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kupiecka 64, 65-058 Zielona Góra</t>
+          <t>os. Paderewskiego 64, 40-282 Katowice</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>65-058</t>
+          <t>40-282</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -14273,17 +14273,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>17-03-2018</t>
+          <t>12-10-2018</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -14380,12 +14380,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Zielony Beskid</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ul. Świętojańska 81/41, 81-372 Gdynia</t>
+          <t>ul. Zwycięstwa 81/41, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>81-372</t>
+          <t>44-100</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -14415,12 +14415,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2019-24-04</t>
+          <t>2019-19-11</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-02-06</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-02-06</t>
         </is>
       </c>
     </row>
@@ -14522,12 +14522,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o. o.</t>
+          <t>Zielony Bieszczady sp. z o. o.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 38</t>
+          <t>ul Krupówki 38</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -14557,12 +14557,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>20200503</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -14664,12 +14664,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Helios Markets Sp. z o.o.</t>
+          <t>Zielony Karpaty Sp. z o.o.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ulica Bolesława Prusa 115, 05-800 Pruszków</t>
+          <t>ulica Najświętszej Maryi Panny 115, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>05-800</t>
+          <t>42-200</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>10/06/2021</t>
+          <t>05/01/2021</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -14734,7 +14734,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>0000009902</t>
+          <t>000000990</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -14806,12 +14806,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lumen Advisory SP Z O O</t>
+          <t>Zielony Bałtyk SP Z O O</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Kościuszki 132, 05-500 Piaseczno</t>
+          <t>11 Listopada 132, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>05-500</t>
+          <t>43-300</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -14841,12 +14841,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2022/17/07</t>
+          <t>2022/12/02</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2022-01-07</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
@@ -14948,12 +14948,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nova Data spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Sudety spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 149/3, 32-020 Wieliczka</t>
+          <t>149/3, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>32-020</t>
+          <t>36-047</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -14983,12 +14983,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>24-08-2023</t>
+          <t>19-03-2023</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -15090,12 +15090,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ul Dąbrowskiego 166, 32-600 Oświęcim</t>
+          <t>ul Franciszkańska 166, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>32-600</t>
+          <t>37-700</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -15125,12 +15125,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-26-04</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -15232,12 +15232,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Polaris Capital S.A.</t>
+          <t>Niebieski Bizon S.A.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ulica Rynek 3, 38-400 Krosno</t>
+          <t>ulica Kościuszki 3, 38-500 Sanok</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15247,7 +15247,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>38-400</t>
+          <t>38-500</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -15267,12 +15267,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>20251010</t>
+          <t>20250505</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -15374,12 +15374,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Quantum Services SA</t>
+          <t>Niebieski Canyon SA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Mickiewicza 20, 39-300 Mielec</t>
+          <t>Suraska 20, 15-422 Białystok</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>39-300</t>
+          <t>15-422</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -15409,12 +15409,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>17/11/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>FULLY_CORROOBRATED</t>
+          <t>FULLY_CORROBORATED</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -15459,12 +15459,12 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>IS_DIRECTLY_CONSOLIDATED_BY</t>
+          <t>IS_DIRECLTY_CONSOLIDATED_BY</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTVIE</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -15516,12 +15516,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Silesia Invest S. A.</t>
+          <t>Niebieski Delfin S. A.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ul. Długa 37/55, 58-100 Świdnica</t>
+          <t>37/55, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15531,7 +15531,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>58-100</t>
+          <t>16-030</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -15551,12 +15551,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2015/24/12</t>
+          <t>2015/19/07</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
+          <t>2015-12-08</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
@@ -15653,17 +15653,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>6299O0CO0CO0CO0CO050</t>
+          <t>5299O0CO0CO0CO0CO050</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka Akcyjna</t>
+          <t>Niebieski Echo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ul Wojska Polskiego 54, 57-300 Kłodzko</t>
+          <t>ul 3 Maja 54, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15673,7 +15673,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>57-300</t>
+          <t>17-200</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -15693,12 +15693,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>03-01-2016</t>
+          <t>26-08-2016</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -15800,12 +15800,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Astra Finance sp. z o.o.</t>
+          <t>Niebieski Falcon sp. z o.o.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ulica Chrobrego 71, 62-200 Gniezno</t>
+          <t>ulica os. LSM 71, 20-400 Lublin</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15815,7 +15815,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>62-200</t>
+          <t>20-400</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2017-10-02</t>
+          <t>2017-05-09</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -15942,12 +15942,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Niebieski Gryf sp z oo</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Słowiańska 88, 64-100 Leszno</t>
+          <t>88, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>64-100</t>
+          <t>24-120</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -15977,12 +15977,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>20180317</t>
+          <t>20181012</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -16012,7 +16012,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>343753932</t>
+          <t>243753932</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -16084,12 +16084,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o. o.</t>
+          <t>Niebieski Horyzont sp. z o. o.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>105/17, 83-110 Tczew</t>
+          <t>ul. Brzeska 105/17, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>83-110</t>
+          <t>21-500</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -16119,12 +16119,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>24/04/2019</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>2019-04-12</t>
+          <t>2019-12-04</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
@@ -16226,12 +16226,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lumen Advisory Sp. z o.o.</t>
+          <t>Niebieski Ikar Sp. z o.o.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ul Sobieskiego 122, 84-200 Wejherowo</t>
+          <t>ul Rynek Staromiejski 122, 87-100 Toruń</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>84-200</t>
+          <t>87-100</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -16261,12 +16261,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>2020/03/05</t>
+          <t>2020/26/12</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -16368,12 +16368,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nova Data SP Z O O</t>
+          <t>Niebieski Jantar SP Z O O</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ulica Głęboka 139, 43-400 Cieszyn</t>
+          <t>ulica Mostowa 139, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>43-400</t>
+          <t>85-110</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -16403,17 +16403,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>10-06-2021</t>
+          <t>05-01-2021</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2021-01-09</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Koral spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Małachowskiego 156, 42-500 Będzin</t>
+          <t>Stare Miasto 156, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16525,7 +16525,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>42-500</t>
+          <t>10-026</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -16545,12 +16545,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2022-17-07</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Lotos Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>os. Królowej Jadwigi 173/69, 88-100 Inowrocław</t>
+          <t>os. Warszawska 173/69, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -16667,7 +16667,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>88-100</t>
+          <t>11-700</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>20230824</t>
+          <t>20230319</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -16794,12 +16794,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quantum Services S.A.</t>
+          <t>Niebieski Magnolia S.A.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ul Wybickiego 10, 86-300 Grudziądz</t>
+          <t>ul Wojska Polskiego 10, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16809,7 +16809,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>86-300</t>
+          <t>70-470</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -16829,12 +16829,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>03/09/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Silesia Invest SA</t>
+          <t>Niebieski Neon SA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -16971,12 +16971,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>2025/10/10</t>
+          <t>2025/05/05</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -17078,12 +17078,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Vistula Fintech S. A.</t>
+          <t>Niebieski Oaza S. A.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Długa 164, Brzeg</t>
+          <t>Ogarna 164, Gdańsk</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -17113,17 +17113,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>17-11-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ul. Lubelska 61/31, 24-100 Puławy</t>
+          <t>ul. Byczyńska 61/31, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17235,7 +17235,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>24-100</t>
+          <t>46-200</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -17255,12 +17255,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>2015-24-12</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -17315,7 +17315,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -17350,7 +17350,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
     </row>
@@ -17362,12 +17362,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Niebieski Rubin sp. z o.o.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ul Staszica 78, 22-400 Zamość</t>
+          <t>ul Chrobrego 78, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -17377,7 +17377,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>22-400</t>
+          <t>66-400</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -17397,12 +17397,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>20160103</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -17504,12 +17504,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Niebieski Szafir sp z oo</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 95, 16-300 Augustów</t>
+          <t>ulica 30 Stycznia 95, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17519,7 +17519,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>16-300</t>
+          <t>66-300</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -17539,12 +17539,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>10/02/2017</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -17646,12 +17646,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o. o.</t>
+          <t>Niebieski Tytan sp. z o. o.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Kościuszki 112, 16-400 Suwałki</t>
+          <t>Paderewskiego 112, 25-004 Kielce</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>16-400</t>
+          <t>25-004</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -17681,12 +17681,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>2018/17/03</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -17696,7 +17696,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>244783409</t>
+          <t>254704247</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -17771,7 +17771,7 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2018-01-03</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
@@ -17788,12 +17788,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Nova Data Sp. z o.o.</t>
+          <t>Niebieski Uran Sp. z o.o.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ul. Piastowska 129/83, 48-300 Nysa</t>
+          <t>ul. 1 Maja 129/83, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17803,7 +17803,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>48-300</t>
+          <t>28-100</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -17823,12 +17823,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>24-04-2019</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -17930,12 +17930,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Optima Trade SP Z O O</t>
+          <t>Niebieski Wektor SP Z O O</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ul Długa 146, 49-300 Brzeg</t>
+          <t>ul Marszałkowska 146, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17945,7 +17945,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>49-300</t>
+          <t>00-590</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -17965,12 +17965,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-26-12</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -18005,7 +18005,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>6299SKC4WOG80SKC4W71</t>
+          <t>5299SKC4WOG80SKC4W71</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Polaris Capital spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Zefir spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>163, 68-200 Żary</t>
+          <t>ulica Krakowskie Przedmieście 163, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>68-200</t>
+          <t>00-071</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -18107,12 +18107,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>20210610</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -18214,12 +18214,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Żubr Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Sikorskiego 180, 66-200 Świebodzin</t>
+          <t>Floriańska 180, 31-019 Kraków</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>66-200</t>
+          <t>31-019</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18249,12 +18249,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>17/07/2022</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -18351,17 +18351,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5299D83YTOJE94ZUPK91</t>
+          <t>6299D83YTOJE94ZUPK91</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Silesia Invest S.A.</t>
+          <t>Niebieski Sokół S.A.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ul. Armii Krajowej 17/45, 78-100 Kołobrzeg</t>
+          <t>ul. Długa 17/45, 31-147 Kraków</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18371,7 +18371,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>78-100</t>
+          <t>31-147</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -18391,12 +18391,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>2023/24/08</t>
+          <t>2023/19/03</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -18498,12 +18498,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Vistula Fintech SA</t>
+          <t>Niebieski Orzeł SA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 34, 73-110 Stargard</t>
+          <t>ul Piotrkowska 34, 90-102 Łódź</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>73-110</t>
+          <t>90-102</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>03-09-2024</t>
+          <t>26-04-2024</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -18640,12 +18640,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Astra Finance S. A.</t>
+          <t>Niebieski Kormoran S. A.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ulica Mickiewicza 51, 27-600 Sandomierz</t>
+          <t>ulica Zachodnia 51, 90-402 Łódź</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>27-600</t>
+          <t>90-402</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -18675,12 +18675,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -18782,12 +18782,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka Akcyjna</t>
+          <t>Niebieski Barycz Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Sienkiewicza 68, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>Świdnicka 68, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -18797,7 +18797,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>27-400</t>
+          <t>50-066</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -18817,12 +18817,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>20261117</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -18924,12 +18924,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o.o.</t>
+          <t>Niebieski Noteć sp. z o.o.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ul. Marszałkowska 85/7, 00-590 Warszawa</t>
+          <t>ul. Legnicka 85/7, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18939,7 +18939,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>00-590</t>
+          <t>54-203</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>24/12/2015</t>
+          <t>19/07/2015</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
+          <t>2015-08-04</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
@@ -19066,12 +19066,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp z oo</t>
+          <t>Niebieski Pilica sp z oo</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 102, 00-071 Warszawa</t>
+          <t>ul Święty Marcin 102, 61-806 Poznań</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19081,7 +19081,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>00-071</t>
+          <t>61-806</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -19101,12 +19101,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>2016/03/01</t>
+          <t>2016/26/08</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -19136,7 +19136,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>245575305</t>
+          <t>255496147</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -19208,12 +19208,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o. o.</t>
+          <t>Niebieski Narew sp. z o. o.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ulica Floriańska 119, 31-019 Kraków</t>
+          <t>ulica Głogowska 119, 60-734 Poznań</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19223,7 +19223,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>31-019</t>
+          <t>60-734</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -19243,17 +19243,17 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>10-02-2017</t>
+          <t>05-09-2017</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2017-01-05</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -19350,12 +19350,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Optima Trade Sp. z o.o.</t>
+          <t>Niebieski Jodełka Sp. z o.o.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Długa 136, 31-147 Kraków</t>
+          <t>Długa 136, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>31-147</t>
+          <t>80-831</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -19385,12 +19385,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>2018-17-03</t>
+          <t>2018-12-10</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -19492,12 +19492,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Niebieski Kaktus SP Z O O</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 153/59, 90-102 Łódź</t>
+          <t>ul. Grunwaldzka 153/59, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19507,7 +19507,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>90-102</t>
+          <t>80-236</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -19527,12 +19527,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>20190424</t>
+          <t>20191119</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -19634,12 +19634,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Quantum Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Szmaragd spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>80-236 Gdańsk</t>
+          <t>21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>80-236</t>
+          <t>21-500</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -19669,12 +19669,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>03/05/2020</t>
+          <t>26/12/2020</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -19704,7 +19704,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>245892069</t>
+          <t>255812909</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-01-11</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
@@ -19776,12 +19776,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Topaz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 7, 50-066 Wrocław</t>
+          <t>ulica Wyszyńskiego 7, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>50-066</t>
+          <t>70-200</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -19811,12 +19811,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>2021/10/06</t>
+          <t>2021/05/01</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -19918,12 +19918,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Niebieski Granit S.A.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Legnicka 24, 54-203 Wrocław</t>
+          <t>Mariacka 24, 40-014 Katowice</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>54-203</t>
+          <t>40-014</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -19953,17 +19953,17 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>17-07-2022</t>
+          <t>12-02-2022</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -20060,12 +20060,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>P.P.H.U. Astra Finance</t>
+          <t>P.P.H.U. Niebieski Marmur</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 41/21, 61-806 Poznań</t>
+          <t>ul. Warszawska 41/21, 40-009 Katowice</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20075,7 +20075,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>61-806</t>
+          <t>40-009</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -20095,12 +20095,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>2023-24-08</t>
+          <t>2023-19-03</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -20202,12 +20202,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S. A.</t>
+          <t>Niebieski Syrena S. A.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ul Głogowska 58, 60-734 Poznań</t>
+          <t>ul Krakowskie Przedmieście 58, 20-002 Lublin</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20217,7 +20217,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>60-734</t>
+          <t>20-002</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -20237,12 +20237,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>20240903</t>
+          <t>20240426</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -20307,7 +20307,7 @@
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>6299W4CKS08GOW4CKS62</t>
+          <t>5299W4CKS08GOW4CKS62</t>
         </is>
       </c>
       <c r="X143" t="inlineStr">
@@ -20344,12 +20344,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka Akcyjna</t>
+          <t>Niebieski Zodiak Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ulica Długa 75, 80-831 Gdańsk</t>
+          <t>ulica Narutowicza 75, 20-004 Lublin</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -20359,7 +20359,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>80-831</t>
+          <t>20-004</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -20379,12 +20379,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -20486,12 +20486,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o.o.</t>
+          <t>Niebieski Olimp sp. z o.o.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Grunwaldzka 92, 80-236 Gdańsk</t>
+          <t>Lipowa 92, 15-424 Białystok</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -20501,7 +20501,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>80-236</t>
+          <t>15-424</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -20521,12 +20521,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>2026/17/11</t>
+          <t>2026/12/06</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -20611,7 +20611,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
@@ -20628,12 +20628,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Niebieski Zorza sp z oo</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 109/73, 70-435 Szczecin</t>
+          <t>ul. Sienkiewicza 109/73, 15-092 Białystok</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -20643,7 +20643,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>70-435</t>
+          <t>15-092</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -20663,12 +20663,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>24-12-2015</t>
+          <t>19-07-2015</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -20770,12 +20770,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o. o.</t>
+          <t>Niebieski Krokus sp. z o. o.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>os. Wyszyńskiego 126, 70-200 Szczecin</t>
+          <t>os. Gdańska 126, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -20785,7 +20785,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>70-200</t>
+          <t>85-005</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -20805,12 +20805,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-26-08</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -20912,12 +20912,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Polaris Capital Sp. z o.o.</t>
+          <t>Niebieski Narcyz Sp. z o.o.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ulica Mariacka 143, 40-014 Katowice</t>
+          <t>ulica Dworcowa 143, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>40-014</t>
+          <t>85-009</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -20947,12 +20947,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>20170210</t>
+          <t>20170905</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Quantum Services SP Z O O</t>
+          <t>Niebieski Giewont SP Z O O</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Warszawska 160, 40-009 Katowice</t>
+          <t>Szeroka 160, 87-100 Toruń</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -21069,7 +21069,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>40-009</t>
+          <t>87-100</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -21089,12 +21089,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>17/03/2018</t>
+          <t>12/10/2018</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -21196,12 +21196,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Silesia Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 177/35, 20-002 Lublin</t>
+          <t>ul. Chełmińska 177/35, 87-100 Toruń</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -21211,7 +21211,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>20-002</t>
+          <t>87-100</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -21231,12 +21231,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>2019/24/04</t>
+          <t>2019/19/11</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -21321,7 +21321,7 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2019-08-04</t>
+          <t>2019-04-08</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
@@ -21338,12 +21338,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Kasprowy Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ul Narutowicza 14, 20-004 Lublin</t>
+          <t>ul 3 Maja 14, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -21353,7 +21353,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>20-004</t>
+          <t>35-030</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -21373,12 +21373,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>03-05-2020</t>
+          <t>26-12-2020</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -21480,12 +21480,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Astra Finance S.A.</t>
+          <t>Amber Budownictwo S.A.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ulica Lipowa 31, 15-424 Białystok</t>
+          <t>ulica Piłsudskiego 31, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -21495,7 +21495,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>15-424</t>
+          <t>35-074</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -21515,27 +21515,27 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>20210901</t>
+          <t/>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>02/10/2021</t>
+          <t/>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>529900T8BM49AURSDO55</t>
+          <t/>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -21622,12 +21622,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SA</t>
+          <t>Amber Transport SA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Sienkiewicza 48, 15-092 Białystok</t>
+          <t>Sienkiewicza 48, 25-007 Kielce</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -21637,7 +21637,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>15-092</t>
+          <t>25-007</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -21657,12 +21657,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>20220717</t>
+          <t>20220212</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -21692,7 +21692,7 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>246921531</t>
+          <t>346921531</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
@@ -21764,12 +21764,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Helios Markets S. A.</t>
+          <t>Amber Spedycja S. A.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ul. Gdańska 65/87, 85-005 Bydgoszcz</t>
+          <t>ul. Warszawska 65/87, 25-512 Kielce</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -21779,7 +21779,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>85-005</t>
+          <t>25-512</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>24/08/2023</t>
+          <t>19/03/2023</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -21906,12 +21906,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>Amber Logistyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ul Dworcowa 82, 85-009 Bydgoszcz</t>
+          <t>ul Kościuszki 82, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -21921,7 +21921,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>85-009</t>
+          <t>10-504</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -21941,12 +21941,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>03/09/2024 08:14</t>
+          <t>26/04/2024 08:14</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -22048,12 +22048,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o.o.</t>
+          <t>Amber Handel sp. z o.o.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ulica Szeroka 99, 87-100 Toruń</t>
+          <t>ulica Dąbrowszczaków 99, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -22063,7 +22063,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>87-100</t>
+          <t>10-540</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -22083,12 +22083,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>10-10-2025</t>
+          <t>05-05-2025</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -22190,12 +22190,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Amber Usługi sp z oo</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Chełmińska 116, 87-100 Toruń</t>
+          <t>Krakowska 116, 45-018 Opole</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -22205,7 +22205,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>87-100</t>
+          <t>45-018</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -22225,12 +22225,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>2026-17-11</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -22332,12 +22332,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o. o.</t>
+          <t>Amber Finanse sp. z o. o.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 133/49, 35-030 Rzeszów</t>
+          <t>ul. Ozimska 133/49, 45-057 Opole</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -22347,7 +22347,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>35-030</t>
+          <t>45-057</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -22367,12 +22367,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>20151224</t>
+          <t>20150719</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -22474,12 +22474,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Quantum Services Sp. z o.o.</t>
+          <t>Amber Doradztwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 150, 35-074 Rzeszów</t>
+          <t>ul Bohaterów Westerplatte 150, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -22489,7 +22489,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>35-074</t>
+          <t>65-034</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -22504,17 +22504,17 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>sp. z o.o.</t>
+          <t>s. z o.o.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>03/01/2016</t>
+          <t>26/08/2016</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>529900T8BM49AURSDO55</t>
+          <t>529900T8B49UARSDO55</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>PARTIALLY_CORROBORATED</t>
+          <t>PARTIALLY_CORORBORATED</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -22564,7 +22564,7 @@
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>ACITVE</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="U159" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>2016-11-09</t>
+          <t>2016-09-11</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
@@ -22611,17 +22611,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>62997WLAZOD2RG5UJ835</t>
+          <t>52997WLAZOD2RG5UJ835</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Amber Szkolenia SP Z O O</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 167, 25-007 Kielce</t>
+          <t>ulica Kupiecka 167, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>25-007</t>
+          <t>65-058</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -22651,12 +22651,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>2017/10/02</t>
+          <t>2017/05/09</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -22666,7 +22666,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2017-02-06</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -22758,12 +22758,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Vistula Fintech spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Media spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Warszawska 4, 25-512 Kielce</t>
+          <t>Świętojańska 4, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -22773,7 +22773,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>25-512</t>
+          <t>81-372</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -22793,17 +22793,17 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>17-03-2018</t>
+          <t>12-10-2018</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -22905,7 +22905,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 21/11, 10-504 Olsztyn</t>
+          <t>ul. 10 Lutego 21/11, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -22915,7 +22915,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>10-504</t>
+          <t>81-364</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -22935,12 +22935,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>2019-24-04</t>
+          <t>2019-19-11</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-02-06</t>
         </is>
       </c>
       <c r="V162" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-02-06</t>
         </is>
       </c>
     </row>
@@ -23042,12 +23042,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Amber Marketing S.A.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ul Dąbrowszczaków 38, 10-540 Olsztyn</t>
+          <t>ul Bolesława Prusa 38, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -23057,7 +23057,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>10-540</t>
+          <t>05-800</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -23077,12 +23077,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>20200503</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -23112,7 +23112,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>347713438</t>
+          <t>247713438</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
@@ -23184,12 +23184,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Helios Markets SA</t>
+          <t>Amber Druk SA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ulica Krakowska 55, 45-018 Opole</t>
+          <t>ulica Kościuszki 55, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>45-018</t>
+          <t>05-500</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -23219,12 +23219,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>10/06/2021</t>
+          <t>05/01/2021</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -23326,12 +23326,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Lumen Advisory S. A.</t>
+          <t>Amber Informatyka S. A.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ozimska 72, 45-057 Opole</t>
+          <t>Sienkiewicza 72, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>45-057</t>
+          <t>32-020</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -23361,12 +23361,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>2022/17/07</t>
+          <t>2022/12/02</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -23376,7 +23376,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -23451,7 +23451,7 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2022-01-07</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
@@ -23468,12 +23468,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Amber Oprogramowanie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Westerplatte 89/63, 65-034 Zielona Góra</t>
+          <t>ul. Dąbrowskiego 89/63, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -23483,7 +23483,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>65-034</t>
+          <t>32-600</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -23503,12 +23503,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>24-08-2023</t>
+          <t>19-03-2023</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -23610,12 +23610,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o.o.</t>
+          <t>Amber Rolnictwo sp. z o.o.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ul Kupiecka 106, 65-058 Zielona Góra</t>
+          <t>ul Rynek 106, 38-400 Krosno</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -23625,7 +23625,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>65-058</t>
+          <t>38-400</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -23645,12 +23645,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-26-04</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -23752,12 +23752,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Amber Ogrodnictwo sp z oo</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ulica Świętojańska 123, 81-372 Gdynia</t>
+          <t>ulica Mickiewicza 123, 39-300 Mielec</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -23767,7 +23767,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>81-372</t>
+          <t>39-300</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -23787,12 +23787,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>20251010</t>
+          <t>20250505</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -23894,12 +23894,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o. o.</t>
+          <t>Amber Produkcja sp. z o. o.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>10 Lutego 140, 81-364 Gdynia</t>
+          <t>Długa 140, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -23909,7 +23909,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>81-364</t>
+          <t>58-100</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -23929,12 +23929,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>17/11/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -24036,12 +24036,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Silesia Invest Sp. z o.o.</t>
+          <t>Amber Przemysł Sp. z o.o.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ul. Bolesława Prusa 157/25, 05-800 Pruszków</t>
+          <t>157/25, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -24051,7 +24051,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>05-800</t>
+          <t>57-300</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -24071,12 +24071,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>2015/24/12</t>
+          <t>2015/19/07</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -24161,7 +24161,7 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
+          <t>2015-12-08</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
@@ -24178,12 +24178,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Vistula Fintech SP Z O O</t>
+          <t>Amber Ekologia SP Z O O</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ul Kościuszki 174, 05-500 Piaseczno</t>
+          <t>ul Chrobrego 174, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -24193,7 +24193,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>05-500</t>
+          <t>62-200</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -24213,12 +24213,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>03-01-2016</t>
+          <t>26-08-2016</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -24320,12 +24320,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Astra Finance spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Energetyka spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 11, 32-020 Wieliczka</t>
+          <t>ulica Słowiańska 11, 64-100 Leszno</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -24335,7 +24335,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>32-020</t>
+          <t>64-100</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -24355,12 +24355,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>2017-10-02</t>
+          <t>2017-05-09</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -24462,12 +24462,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Instalacje Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Dąbrowskiego 28, 32-600 Oświęcim</t>
+          <t>Gdańska 28, 83-110 Tczew</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -24477,7 +24477,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>32-600</t>
+          <t>83-110</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -24497,12 +24497,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>20180317</t>
+          <t>20181012</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -24604,12 +24604,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Amber Nieruchomości S.A.</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>ul. Rynek 45/77, 38-400 Krosno</t>
+          <t>ul. Sobieskiego 45/77, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -24619,7 +24619,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>38-400</t>
+          <t>84-200</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -24639,12 +24639,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>24/04/2019</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -24704,7 +24704,7 @@
       </c>
       <c r="V174" t="inlineStr">
         <is>
-          <t>2019-04-12</t>
+          <t>2019-12-04</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
@@ -24746,12 +24746,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Lumen Advisory SA</t>
+          <t>Amber Inwestycje SA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 62, 39-300 Mielec</t>
+          <t>ul Głęboka 62, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -24761,7 +24761,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>39-300</t>
+          <t>43-400</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -24781,12 +24781,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2020/03/05</t>
+          <t>2020/26/12</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -24888,12 +24888,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Nova Data S. A.</t>
+          <t>Amber Medycyna S. A.</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>os. Długa 79, 58-100 Świdnica</t>
+          <t>os. Małachowskiego 79, 42-500 Będzin</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -24903,7 +24903,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>58-100</t>
+          <t>42-500</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -24923,17 +24923,17 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>10-06-2021</t>
+          <t>05-01-2021</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2021-01-09</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -24963,7 +24963,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>6299BGLQV05AFKPUZ498</t>
+          <t>5299BGLQV05AFKPUZ498</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -25030,12 +25030,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Amber Zdrowie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>96, 57-300 Kłodzko</t>
+          <t>Królowej Jadwigi 96, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -25045,7 +25045,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>57-300</t>
+          <t>88-100</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -25065,12 +25065,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2022-17-07</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -25172,12 +25172,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Amber Urody sp. z o.o.</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ul. Chrobrego 113/39, 62-200 Gniezno</t>
+          <t>ul. Wybickiego 113/39, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -25187,7 +25187,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>62-200</t>
+          <t>86-300</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -25207,12 +25207,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>20230824</t>
+          <t>20230319</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -25314,12 +25314,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Amber Turystyka sp z oo</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ul Słowiańska 130, 64-100 Leszno</t>
+          <t>ul Czarnieckiego 130, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>64-100</t>
+          <t>14-100</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -25349,12 +25349,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>03/09/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -25414,7 +25414,7 @@
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
@@ -25456,12 +25456,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o. o.</t>
+          <t>Amber Rozrywka sp. z o. o.</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ulica Gdańska 147, 83-110 Tczew</t>
+          <t>ulica Warszawska 147, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>83-110</t>
+          <t>11-500</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -25491,12 +25491,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>2025/10/10</t>
+          <t>2025/05/05</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -25598,12 +25598,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Vistula Fintech Sp. z o.o.</t>
+          <t>Amber Gastronomia Sp. z o.o.</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sobieskiego 164, 84-200 Wejherowo</t>
+          <t>Lubelska 164, 24-100 Puławy</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>84-200</t>
+          <t>24-100</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -25633,17 +25633,17 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>17-11-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -25668,7 +25668,7 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>249218045</t>
+          <t>259138887</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
@@ -25740,12 +25740,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Amber Moda</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ul. Głęboka 1/1, 43-400 Cieszyn</t>
+          <t>ul. Staszica 1/1, 22-400 Zamość</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -25755,7 +25755,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>43-400</t>
+          <t>22-400</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -25775,12 +25775,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>2015-24-12</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -25835,7 +25835,7 @@
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="V182" t="inlineStr">
@@ -25870,7 +25870,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2015-10-06</t>
         </is>
       </c>
     </row>
@@ -25882,12 +25882,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Baltic Med Supply spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Tekstylia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ul Małachowskiego 18, 42-500 Będzin</t>
+          <t>ul 3 Maja 18, 16-300 Augustów</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -25897,7 +25897,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>42-500</t>
+          <t>16-300</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -25917,12 +25917,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>20160103</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -26024,12 +26024,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Motoryzacja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ulica Królowej Jadwigi 35, 88-100 Inowrocław</t>
+          <t>ulica Kościuszki 35, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -26039,7 +26039,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>88-100</t>
+          <t>16-400</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -26059,12 +26059,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>10/02/2017</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -26166,12 +26166,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Amber Ubezpieczenia S.A.</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>os. Kościuszki 172, 16-400</t>
+          <t>os. Kupiecka 172, 65-058</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -26181,7 +26181,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>16-400</t>
+          <t>65-058</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -26201,12 +26201,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>2018/17/03</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -26216,7 +26216,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2018-01-03</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr">
@@ -26308,12 +26308,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Nova Data SA</t>
+          <t>Amber Spawalnictwo SA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>ul. Czarnieckiego 69/53, 14-100 Ostróda</t>
+          <t>ul. Długa 69/53, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -26323,7 +26323,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>14-100</t>
+          <t>49-300</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -26343,12 +26343,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>24-04-2019</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -26450,12 +26450,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Optima Trade S. A.</t>
+          <t>Amber Ślusarstwo S. A.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ul Warszawska 86, 11-500 Giżycko</t>
+          <t>ul Rynek 86, 68-200 Żary</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -26465,7 +26465,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>11-500</t>
+          <t>68-200</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -26485,12 +26485,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-26-12</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -26592,12 +26592,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka Akcyjna</t>
+          <t>Amber Krawiectwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ulica Lubelska 103, 24-100 Puławy</t>
+          <t>ulica Sikorskiego 103, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -26607,7 +26607,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>24-100</t>
+          <t>66-200</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -26627,12 +26627,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>20210610</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -26734,12 +26734,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Amber Ochrona sp. z o.o.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Staszica 120, 22-400 Zamość</t>
+          <t>Armii Krajowej 120, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -26749,7 +26749,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>22-400</t>
+          <t>78-100</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -26769,12 +26769,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>17/07/2022</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -26876,12 +26876,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Amber Catering sp z oo</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 137/15, 16-300 Augustów</t>
+          <t>ul. Piłsudskiego 137/15, 73-110 Stargard</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -26891,7 +26891,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>16-300</t>
+          <t>73-110</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -26911,12 +26911,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>2023/24/08</t>
+          <t>2023/19/03</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -27018,12 +27018,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o. o.</t>
+          <t>Amber Księgowość sp. z o. o.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ul Kościuszki 154, 16-400 Suwałki</t>
+          <t>154, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -27033,7 +27033,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>16-400</t>
+          <t>27-600</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -27053,12 +27053,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>03-09-2024</t>
+          <t>26-04-2024</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>250009941</t>
+          <t>259930787</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
@@ -27160,12 +27160,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Astra Finance Sp. z o.o.</t>
+          <t>Bizon Budownictwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ulica Piastowska 171, 48-300 Nysa</t>
+          <t>ulica Sienkiewicza 171, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -27175,7 +27175,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>48-300</t>
+          <t>27-400</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -27195,12 +27195,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -27265,7 +27265,7 @@
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>6299F0L6RCXI3O9UF057</t>
+          <t>5299F0L6RCXI3O9UF057</t>
         </is>
       </c>
       <c r="X192" t="inlineStr">
@@ -27302,12 +27302,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Bizon Transport SP Z O O</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Długa 8, 49-300 Brzeg</t>
+          <t>Chmielna 8, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -27317,7 +27317,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>49-300</t>
+          <t>00-020</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -27337,12 +27337,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>20261117</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -27444,12 +27444,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Spedycja spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ul. Rynek 25/67, 68-200 Żary</t>
+          <t>ul. Nowy Świat 25/67, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -27459,7 +27459,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>68-200</t>
+          <t>00-029</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -27479,12 +27479,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>24/12/2015</t>
+          <t>19/07/2015</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -27544,7 +27544,7 @@
       </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
+          <t>2015-08-04</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
@@ -27586,12 +27586,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Logistyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ul Sikorskiego 42, 66-200 Świebodzin</t>
+          <t>ul os. Przyjaźń 42, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -27601,7 +27601,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>66-200</t>
+          <t>01-355</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -27621,12 +27621,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>2016/03/01</t>
+          <t>2016/26/08</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -27728,12 +27728,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Nova Data S.A.</t>
+          <t>Bizon Handel S.A.</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ulica Armii Krajowej 59, 78-100 Kołobrzeg</t>
+          <t>ulica Jagiellońska 59, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -27743,7 +27743,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>78-100</t>
+          <t>05-120</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -27763,17 +27763,17 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>10-02-2017</t>
+          <t>05-09-2017</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2017-01-05</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -27833,7 +27833,7 @@
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>52997WLAZOD2RG5UJ835</t>
+          <t>62997WLAZOD2RG5UJ835</t>
         </is>
       </c>
       <c r="X196" t="inlineStr">
@@ -27870,12 +27870,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Optima Trade SA</t>
+          <t>Bizon Usługi SA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Piłsudskiego 76, 73-110 Stargard</t>
+          <t>Piłsudskiego 76, 05-270 Marki</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>73-110</t>
+          <t>05-270</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -27905,12 +27905,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>2018-17-03</t>
+          <t>2018-12-10</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -28012,12 +28012,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Polaris Capital S. A.</t>
+          <t>Bizon Finanse S. A.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>93/29, 27-600 Sandomierz</t>
+          <t>ul. Andriollego 93/29, 05-400 Otwock</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -28027,7 +28027,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>27-600</t>
+          <t>05-400</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -28047,12 +28047,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>20190424</t>
+          <t>20191119</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -28154,12 +28154,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka Akcyjna</t>
+          <t>Bizon Doradztwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 110, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>ul Żeromskiego 110, 26-600 Radom</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -28169,7 +28169,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>27-400</t>
+          <t>26-600</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -28189,12 +28189,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>03/05/2020</t>
+          <t>26/12/2020</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -28254,7 +28254,7 @@
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-01-11</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
@@ -28296,12 +28296,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Bizon Szkolenia sp. z o.o.</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 127, 00-590 Warszawa</t>
+          <t>ulica Tumska 127, 09-402 Płock</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -28311,7 +28311,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>00-590</t>
+          <t>09-402</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -28331,12 +28331,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>2021/10/06</t>
+          <t>2021/05/01</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -28438,12 +28438,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Bizon Media sp z oo</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 144, 00-071 Warszawa</t>
+          <t>Karmelicka 144, 31-128 Kraków</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -28453,7 +28453,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>00-071</t>
+          <t>31-128</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -28473,17 +28473,17 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>LAPSED</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>17-07-2022</t>
+          <t>12-02-2022</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">

--- a/data/xlsx/gleif.xlsx
+++ b/data/xlsx/gleif.xlsx
@@ -322,7 +322,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zielony Bieszczady S.A.</t>
+          <t>Pewny Delfin S.A.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -464,7 +464,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zielony Karpaty SA</t>
+          <t>Dobry Koral SA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zielony Bałtyk S. A.</t>
+          <t>Polski Szafir S. A.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zielony Sudety Spółka Akcyjna</t>
+          <t>Europejski Orzeł Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Niebieski Amber sp. z o.o.</t>
+          <t>Globalny Kaktus sp. z o.o.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Niebieski Bizon sp z oo</t>
+          <t>Lokalny Olimp sp z oo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Niebieski Canyon sp. z o. o.</t>
+          <t>Nowoczesny Beskid sp. z o. o.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SP Z  O</t>
+          <t>SP Z O O</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>IS_ULTIMATELY_CONSOLIDATED_BY</t>
+          <t>IS_UTLIMATELY_CNOSOLIDATED_BY</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Niebieski Delfin Sp. z o.o.</t>
+          <t>Tradycyjny Canyon Sp. z o.o.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Niebieski Echo SP Z O O</t>
+          <t>Dynamiczny Jantar SP Z O O</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Niebieski Falcon spółka z ograniczoną odpowiedzialnością</t>
+          <t>Stabilny Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Niebieski Gryf Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Innowacyjny Sokół Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Niebieski Horyzont S.A.</t>
+          <t>Kreatywny Jodełka S.A.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Niebieski Ikar SA</t>
+          <t>Aktywny Zodiak SA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Niebieski Jantar S. A.</t>
+          <t>Jasny Kasprowy S. A.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Niebieski Koral Spółka Akcyjna</t>
+          <t>Green Bizon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Niebieski Lotos sp. z o.o.</t>
+          <t>Blue Ikar sp. z o.o.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Niebieski Magnolia sp z oo</t>
+          <t>Gold Pegaz sp z oo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>IS_ULTIMATELY_CONSOLIDATED_BY</t>
+          <t/>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Niebieski Neon sp. z o. o.</t>
+          <t>Silver Żubr sp. z o. o.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Niebieski Oaza Sp. z o.o.</t>
+          <t>Smart Narew Sp. z o.o.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>P.P.H.U. Niebieski Pegaz</t>
+          <t>P.P.H.U. Fast Syrena</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Niebieski Rubin spółka z ograniczoną odpowiedzialnością</t>
+          <t>Safe Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Niebieski Szafir Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Best Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Niebieski Tytan S.A.</t>
+          <t>Global Horyzont S.A.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Niebieski Uran SA</t>
+          <t>Future Oaza SA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Niebieski Wektor S. A.</t>
+          <t>Wielkopolski Zefir S. A.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Niebieski Zefir Spółka Akcyjna</t>
+          <t>Śląski Pilica Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Niebieski Żubr sp. z o.o.</t>
+          <t>Mazowiecki Marmur sp. z o.o.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Niebieski Sokół sp z oo</t>
+          <t>Pomorski Giewont sp z oo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Niebieski Orzeł sp. z o. o.</t>
+          <t>Dolnośląski Sudety sp. z o. o.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Niebieski Kormoran Sp. z o.o.</t>
+          <t>Karpacki Gryf Sp. z o.o.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Niebieski Barycz SP Z O O</t>
+          <t>Bałtycki Neon SP Z O O</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Niebieski Noteć spółka z ograniczoną odpowiedzialnością</t>
+          <t>Młody Wektor spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Niebieski Pilica Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wspólny Noteć Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Niebieski Narew S.A.</t>
+          <t>Pierwszy Granit S.A.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Niebieski Jodełka SA</t>
+          <t>Zielony Żubr SA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Niebieski Kaktus S. A.</t>
+          <t>Niebieski Narew S. A.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Niebieski Szmaragd Spółka Akcyjna</t>
+          <t>Złoty Syrena Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Niebieski Topaz sp. z o.o.</t>
+          <t>Srebrny Rysy sp. z o.o.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Niebieski Granit sp z oo</t>
+          <t>Czysty Amber sp z oo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Niebieski Syrena Sp. z o.o.</t>
+          <t>Pewny Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Niebieski Zodiak SP Z O O</t>
+          <t>Dobry Zefir SP Z O O</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Niebieski Olimp spółka z ograniczoną odpowiedzialnością</t>
+          <t>Polski Pilica spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Niebieski Zorza Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Europejski Marmur Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Niebieski Krokus S.A.</t>
+          <t>Globalny Giewont S.A.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Niebieski Narcyz SA</t>
+          <t>Lokalny Sudety SA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Niebieski Giewont S. A.</t>
+          <t>Nowoczesny Gryf S. A.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Niebieski Rysy Spółka Akcyjna</t>
+          <t>Tradycyjny Neon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Niebieski Kasprowy sp. z o.o.</t>
+          <t>Dynamiczny Wektor sp. z o.o.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Amber Transport sp. z o. o.</t>
+          <t>Falcon Transport sp. z o. o.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Amber Spedycja Sp. z o.o.</t>
+          <t>Koral Spedycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Amber Logistyka SP Z O O</t>
+          <t>Pegaz Logistyka SP Z O O</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Amber Handel spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wektor Handel spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Amber Usługi Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Usługi Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Amber Finanse S.A.</t>
+          <t>Jodełka Finanse S.A.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Amber Doradztwo SA</t>
+          <t>Marmur Doradztwo SA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>IS_ULTIMATELY_CONSLOIDATED_BY</t>
+          <t>IS_ULTIMATELY_CONSLOIDATED_YB</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Amber Szkolenia S. A.</t>
+          <t>Krokus Szkolenia S. A.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Amber Media Spółka Akcyjna</t>
+          <t>Beskid Media Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8695,7 +8695,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>52990000000000066059</t>
+          <t>62990000000000066059</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Amber Marketing sp z oo</t>
+          <t>Falcon Marketing sp z oo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>62990000000010066177</t>
+          <t>52990000000010066177</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Amber Druk sp. z o. o.</t>
+          <t>Koral Druk sp. z o. o.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Amber Informatyka Sp. z o.o.</t>
+          <t>Pegaz Informatyka Sp. z o.o.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Amber Oprogramowanie SP Z O O</t>
+          <t>Wektor Oprogramowanie SP Z O O</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Amber Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Amber Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Amber Produkcja S.A.</t>
+          <t>Marmur Produkcja S.A.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Amber Przemysł SA</t>
+          <t>Krokus Przemysł SA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Amber Ekologia S. A.</t>
+          <t>Beskid Ekologia S. A.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Amber Instalacje sp. z o.o.</t>
+          <t>Falcon Instalacje sp. z o.o.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Amber Nieruchomości sp z oo</t>
+          <t>Koral Nieruchomości sp z oo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Amber Inwestycje sp. z o. o.</t>
+          <t>Pegaz Inwestycje sp. z o. o.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Amber Medycyna Sp. z o.o.</t>
+          <t>Wektor Medycyna Sp. z o.o.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Amber Zdrowie SP Z O O</t>
+          <t>Kormoran Zdrowie SP Z O O</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10972,7 +10972,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Amber Urody spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Urody spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Amber Turystyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Turystyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Amber Rozrywka S.A.</t>
+          <t>Krokus Rozrywka S.A.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Amber Gastronomia SA</t>
+          <t>Beskid Gastronomia SA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Amber Tekstylia Spółka Akcyjna</t>
+          <t>Falcon Tekstylia Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Amber Motoryzacja sp. z o.o.</t>
+          <t>Koral Motoryzacja sp. z o.o.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>sp z oo</t>
+          <t/>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t/>
+          <t>National Court Register (Ministry of Justice) | Krajowy Rejestr Sadowy (KRS) (Ministerstwo Sprawiedliwosci) | Poland | RA000466</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Amber Ubezpieczenia sp z oo</t>
+          <t>Pegaz Ubezpieczenia sp z oo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Amber Spawalnictwo sp. z o. o.</t>
+          <t>Wektor Spawalnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Amber Ślusarstwo Sp. z o.o.</t>
+          <t>Kormoran Ślusarstwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Amber Krawiectwo SP Z O O</t>
+          <t>Jodełka Krawiectwo SP Z O O</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Amber Ochrona spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Ochrona spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Amber Catering Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Krokus Catering Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Amber Księgowość S.A.</t>
+          <t>Beskid Księgowość S.A.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -12960,7 +12960,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bizon Budownictwo SA</t>
+          <t>Jantar Budownictwo SA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bizon Transport S. A.</t>
+          <t>Oaza Transport S. A.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bizon Spedycja Spółka Akcyjna</t>
+          <t>Uran Spedycja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bizon Logistyka sp. z o.o.</t>
+          <t>Orzeł Logistyka sp. z o.o.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -13528,7 +13528,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bizon Handel sp z oo</t>
+          <t>Narew Handel sp z oo</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bizon Usługi sp. z o. o.</t>
+          <t>Granit Usługi sp. z o. o.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -13812,7 +13812,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bizon Finanse Sp. z o.o.</t>
+          <t>Zorza Finanse Sp. z o.o.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Bizon Doradztwo SP Z O O</t>
+          <t>Kasprowy Doradztwo SP Z O O</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bizon Szkolenia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sudety Szkolenia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -14238,7 +14238,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bizon Media Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Media Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>P.P.H.U. Bizon Reklama</t>
+          <t>P.P.H.U. Jantar Reklama</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bizon Marketing SA</t>
+          <t>Oaza Marketing SA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -14664,7 +14664,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Bizon Druk S. A.</t>
+          <t>Uran Druk S. A.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bizon Informatyka Spółka Akcyjna</t>
+          <t>Orzeł Informatyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Bizon Oprogramowanie sp. z o.o.</t>
+          <t>Narew Oprogramowanie sp. z o.o.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Bizon Rolnictwo sp z oo</t>
+          <t>Granit Rolnictwo sp z oo</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bizon Ogrodnictwo sp. z o. o.</t>
+          <t>Zorza Ogrodnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bizon Produkcja Sp. z o.o.</t>
+          <t>Kasprowy Produkcja Sp. z o.o.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -15384,7 +15384,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Pozna</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -15429,7 +15429,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>5299008MB49AURSOD55</t>
+          <t>5299008MB49AURSDO55</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>IS_UTLIMATELY_CONSOLIDATED_BY</t>
+          <t>IS_ULTIMATELY_CONSOLIDATED_BY</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
@@ -15516,7 +15516,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bizon Przemysł SP Z O O</t>
+          <t>Sudety Przemysł SP Z O O</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -15658,7 +15658,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bizon Ekologia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Ekologia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -15800,7 +15800,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Bizon Energetyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jantar Energetyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Bizon Instalacje S.A.</t>
+          <t>Oaza Instalacje S.A.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Bizon Nieruchomości SA</t>
+          <t>Uran Nieruchomości SA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Bizon Inwestycje S. A.</t>
+          <t>Orzeł Inwestycje S. A.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Bizon Medycyna Spółka Akcyjna</t>
+          <t>Narew Medycyna Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -16510,7 +16510,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bizon Zdrowie sp. z o.o.</t>
+          <t>Granit Zdrowie sp. z o.o.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bizon Urody sp z oo</t>
+          <t>Zorza Urody sp z oo</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Bizon Turystyka sp. z o. o.</t>
+          <t>Kasprowy Turystyka sp. z o. o.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Bizon Rozrywka Sp. z o.o.</t>
+          <t>Sudety Rozrywka Sp. z o.o.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Bizon Gastronomia SP Z O O</t>
+          <t>Echo Gastronomia SP Z O O</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -17362,7 +17362,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Bizon Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Oaza Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -17504,7 +17504,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Bizon Motoryzacja S.A.</t>
+          <t>Uran Motoryzacja S.A.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -17646,7 +17646,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Bizon Ubezpieczenia SA</t>
+          <t>Orzeł Ubezpieczenia SA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -17788,7 +17788,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Bizon Spawalnictwo S. A.</t>
+          <t>Narew Spawalnictwo S. A.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -17930,7 +17930,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Bizon Ślusarstwo Spółka Akcyjna</t>
+          <t>Granit Ślusarstwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bizon Krawiectwo sp. z o.o.</t>
+          <t>Zorza Krawiectwo sp. z o.o.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -18147,7 +18147,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>52990000000010072676</t>
+          <t>62990000000010072676</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bizon Ochrona sp z oo</t>
+          <t>Kasprowy Ochrona sp z oo</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -18351,12 +18351,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>62990000000000072849</t>
+          <t>52990000000000072849</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Bizon Catering sp. z o. o.</t>
+          <t>Sudety Catering sp. z o. o.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -18498,7 +18498,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bizon Księgowość Sp. z o.o.</t>
+          <t>Echo Księgowość Sp. z o.o.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -18640,7 +18640,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Canyon Budownictwo SP Z O O</t>
+          <t>Tytan Budownictwo SP Z O O</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -18782,7 +18782,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Canyon Transport spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sokół Transport spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -18924,7 +18924,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Canyon Spedycja Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Spedycja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -19066,7 +19066,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Canyon Logistyka S.A.</t>
+          <t>Topaz Logistyka S.A.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Canyon Handel SA</t>
+          <t>Olimp Handel SA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -19350,7 +19350,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Canyon Usługi S. A.</t>
+          <t>Rysy Usługi S. A.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -19492,7 +19492,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Canyon Finanse Spółka Akcyjna</t>
+          <t>Bałtyk Finanse Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Canyon Doradztwo sp. z o.o.</t>
+          <t>Delfin Doradztwo sp. z o.o.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Canyon Szkolenia sp z oo</t>
+          <t>Ikar Szkolenia sp z oo</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -19918,7 +19918,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Canyon Media sp. z o. o.</t>
+          <t>Neon Media sp. z o. o.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -20060,7 +20060,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PPHU Canyon Reklama</t>
+          <t>PPHU Tytan Reklama</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Canyon Marketing SP Z O O</t>
+          <t>Sokół Marketing SP Z O O</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Canyon Druk spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Druk spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -20486,7 +20486,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Canyon Informatyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Informatyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Canyon Oprogramowanie S.A.</t>
+          <t>Olimp Oprogramowanie S.A.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -20770,7 +20770,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Canyon Rolnictwo SA</t>
+          <t>Rysy Rolnictwo SA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -20912,7 +20912,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Canyon Ogrodnictwo S. A.</t>
+          <t>Bałtyk Ogrodnictwo S. A.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Canyon Produkcja Spółka Akcyjna</t>
+          <t>Delfin Produkcja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -21196,7 +21196,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Canyon Przemysł sp. z o.o.</t>
+          <t>Ikar Przemysł sp. z o.o.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -21338,7 +21338,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Canyon Ekologia sp z oo</t>
+          <t>Neon Ekologia sp z oo</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Canyon Energetyka sp. z o. o.</t>
+          <t>Tytan Energetyka sp. z o. o.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -21622,7 +21622,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Canyon Instalacje Sp. z o.o.</t>
+          <t>Sokół Instalacje Sp. z o.o.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -21764,7 +21764,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Canyon Nieruchomości SP Z O O</t>
+          <t>Pilica Nieruchomości SP Z O O</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -21906,7 +21906,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Canyon Inwestycje spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Inwestycje spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -22048,7 +22048,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Canyon Medycyna Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Medycyna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -22190,7 +22190,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Canyon Zdrowie S.A.</t>
+          <t>Rysy Zdrowie S.A.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -22332,7 +22332,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Canyon Urody SA</t>
+          <t>Bałtyk Urody SA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -22474,7 +22474,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Canyon Turystyka S. A.</t>
+          <t>Delfin Turystyka S. A.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>529900T8B49AURSDO55</t>
+          <t>529900T8B49UARSDO55</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>PRATIALLY_CORORBORATED</t>
+          <t>PARTIALLY_CORORBORATED</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Vsitula Fintech S.A.</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -22589,7 +22589,7 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>IS_ULTIMATELY_CONSOLIDATED_BY</t>
+          <t>IS_ULTIMATELY_CONSLOIDATED_BY</t>
         </is>
       </c>
       <c r="Z159" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Canyon Rozrywka Spółka Akcyjna</t>
+          <t>Ikar Rozrywka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Canyon Gastronomia sp. z o.o.</t>
+          <t>Neon Gastronomia sp. z o.o.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -23042,7 +23042,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Canyon Tekstylia sp. z o. o.</t>
+          <t>Sokół Tekstylia sp. z o. o.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Canyon Motoryzacja Sp. z o.o.</t>
+          <t>Pilica Motoryzacja Sp. z o.o.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -23326,7 +23326,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Canyon Ubezpieczenia SP Z O O</t>
+          <t>Topaz Ubezpieczenia SP Z O O</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -23468,7 +23468,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Canyon Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -23610,7 +23610,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Canyon Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Rysy Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -23752,7 +23752,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Canyon Krawiectwo S.A.</t>
+          <t>Bałtyk Krawiectwo S.A.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -23894,7 +23894,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Canyon Ochrona SA</t>
+          <t>Delfin Ochrona SA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -24036,7 +24036,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Canyon Catering S. A.</t>
+          <t>Ikar Catering S. A.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -24178,7 +24178,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Canyon Księgowość Spółka Akcyjna</t>
+          <t>Neon Księgowość Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -27549,7 +27549,7 @@
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>52990000000020079293</t>
+          <t>62990000000020079293</t>
         </is>
       </c>
       <c r="X194" t="inlineStr">
@@ -27833,7 +27833,7 @@
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>62990000000020079487</t>
+          <t>52990000000020079487</t>
         </is>
       </c>
       <c r="X196" t="inlineStr">
